--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3433,13 +3433,13 @@
     <t>Practitioner.qualification:exercicePro.period.start</t>
   </si>
   <si>
+    <t>[Donnée restreinte] : Date à partir de laquelle le professionnel exerce cette profession (dateEffetExercice).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.end</t>
+  </si>
+  <si>
     <t>[Donnée restreinte] : Date à partir de laquelle le professionnel n’exerce plus cette profession (dateFinEffetExercice).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.period.end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro.issuer</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -842,8 +842,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -5956,7 +5956,7 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>119</v>
@@ -5968,7 +5968,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -6073,7 +6073,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>119</v>
@@ -6303,7 +6303,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>119</v>
@@ -6533,7 +6533,7 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
@@ -6650,7 +6650,7 @@
         <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>119</v>
@@ -6880,7 +6880,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>119</v>
@@ -7110,7 +7110,7 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
@@ -7227,7 +7227,7 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>119</v>
@@ -7457,7 +7457,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>119</v>
@@ -7689,7 +7689,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -7921,7 +7921,7 @@
         <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>119</v>
@@ -7933,7 +7933,7 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -8274,7 +8274,7 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>119</v>
@@ -8504,7 +8504,7 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>119</v>
@@ -8734,7 +8734,7 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -8851,7 +8851,7 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>119</v>
@@ -9081,7 +9081,7 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>119</v>
@@ -9311,7 +9311,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -9428,7 +9428,7 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>119</v>
@@ -9658,7 +9658,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -9890,7 +9890,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -10122,7 +10122,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -10471,7 +10471,7 @@
         <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>119</v>
@@ -10483,7 +10483,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10588,7 +10588,7 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>119</v>
@@ -10818,7 +10818,7 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>119</v>
@@ -11048,7 +11048,7 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>102</v>
@@ -11165,7 +11165,7 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>119</v>
@@ -11395,7 +11395,7 @@
         <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>119</v>
@@ -11627,7 +11627,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11859,7 +11859,7 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>119</v>
@@ -11871,7 +11871,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -12212,7 +12212,7 @@
         <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>119</v>
@@ -12442,7 +12442,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>119</v>
@@ -12672,7 +12672,7 @@
         <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>102</v>
@@ -12789,7 +12789,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>119</v>
@@ -13019,7 +13019,7 @@
         <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>119</v>
@@ -13249,7 +13249,7 @@
         <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>102</v>
@@ -13481,7 +13481,7 @@
         <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>102</v>
@@ -13947,7 +13947,7 @@
         <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>119</v>
@@ -13959,7 +13959,7 @@
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -14064,7 +14064,7 @@
         <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>119</v>
@@ -14294,7 +14294,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>119</v>
@@ -14526,7 +14526,7 @@
         <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>102</v>
@@ -14643,7 +14643,7 @@
         <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>119</v>
@@ -14873,7 +14873,7 @@
         <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>119</v>
@@ -15105,7 +15105,7 @@
         <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>102</v>
@@ -15222,7 +15222,7 @@
         <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>119</v>
@@ -15452,7 +15452,7 @@
         <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>119</v>
@@ -15684,7 +15684,7 @@
         <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>102</v>
@@ -15801,7 +15801,7 @@
         <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>119</v>
@@ -16031,7 +16031,7 @@
         <v>80</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>119</v>
@@ -16263,7 +16263,7 @@
         <v>90</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>102</v>
@@ -16495,7 +16495,7 @@
         <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>119</v>
@@ -16507,7 +16507,7 @@
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>78</v>
@@ -16848,7 +16848,7 @@
         <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>119</v>
@@ -17078,7 +17078,7 @@
         <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>119</v>
@@ -17310,7 +17310,7 @@
         <v>90</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>102</v>
@@ -17427,7 +17427,7 @@
         <v>80</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>119</v>
@@ -17657,7 +17657,7 @@
         <v>80</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>119</v>
@@ -17889,7 +17889,7 @@
         <v>90</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>102</v>
@@ -18006,7 +18006,7 @@
         <v>80</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>119</v>
@@ -18236,7 +18236,7 @@
         <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>119</v>
@@ -18468,7 +18468,7 @@
         <v>90</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>102</v>
@@ -18700,7 +18700,7 @@
         <v>90</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>102</v>
@@ -29002,7 +29002,7 @@
         <v>80</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>119</v>
@@ -29014,7 +29014,7 @@
         <v>78</v>
       </c>
       <c r="AM221" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN221" t="s" s="2">
         <v>78</v>
@@ -29119,7 +29119,7 @@
         <v>80</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>119</v>
@@ -29349,7 +29349,7 @@
         <v>80</v>
       </c>
       <c r="AI224" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ224" t="s" s="2">
         <v>119</v>
@@ -29579,7 +29579,7 @@
         <v>90</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ226" t="s" s="2">
         <v>102</v>
@@ -29696,7 +29696,7 @@
         <v>80</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ227" t="s" s="2">
         <v>119</v>
@@ -29926,7 +29926,7 @@
         <v>80</v>
       </c>
       <c r="AI229" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ229" t="s" s="2">
         <v>119</v>
@@ -30156,7 +30156,7 @@
         <v>90</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>102</v>
@@ -30273,7 +30273,7 @@
         <v>80</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>119</v>
@@ -30503,7 +30503,7 @@
         <v>80</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ234" t="s" s="2">
         <v>119</v>
@@ -30733,7 +30733,7 @@
         <v>90</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>102</v>
@@ -30965,7 +30965,7 @@
         <v>90</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>102</v>
@@ -31546,7 +31546,7 @@
         <v>80</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ243" t="s" s="2">
         <v>119</v>
@@ -31558,7 +31558,7 @@
         <v>78</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN243" t="s" s="2">
         <v>78</v>
@@ -31663,7 +31663,7 @@
         <v>80</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ244" t="s" s="2">
         <v>102</v>
@@ -31782,7 +31782,7 @@
         <v>80</v>
       </c>
       <c r="AI245" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ245" t="s" s="2">
         <v>102</v>
@@ -31901,7 +31901,7 @@
         <v>80</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ246" t="s" s="2">
         <v>102</v>
@@ -32020,7 +32020,7 @@
         <v>90</v>
       </c>
       <c r="AI247" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ247" t="s" s="2">
         <v>102</v>
@@ -32369,7 +32369,7 @@
         <v>80</v>
       </c>
       <c r="AI250" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ250" t="s" s="2">
         <v>119</v>
@@ -32381,7 +32381,7 @@
         <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -33650,7 +33650,7 @@
         <v>80</v>
       </c>
       <c r="AI261" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ261" t="s" s="2">
         <v>119</v>
@@ -33662,7 +33662,7 @@
         <v>78</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>78</v>
@@ -33767,7 +33767,7 @@
         <v>80</v>
       </c>
       <c r="AI262" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ262" t="s" s="2">
         <v>102</v>
@@ -33886,7 +33886,7 @@
         <v>80</v>
       </c>
       <c r="AI263" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ263" t="s" s="2">
         <v>102</v>
@@ -34005,7 +34005,7 @@
         <v>80</v>
       </c>
       <c r="AI264" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ264" t="s" s="2">
         <v>102</v>
@@ -34124,7 +34124,7 @@
         <v>90</v>
       </c>
       <c r="AI265" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ265" t="s" s="2">
         <v>102</v>
@@ -34473,7 +34473,7 @@
         <v>80</v>
       </c>
       <c r="AI268" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ268" t="s" s="2">
         <v>119</v>
@@ -34485,7 +34485,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -35754,7 +35754,7 @@
         <v>80</v>
       </c>
       <c r="AI279" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ279" t="s" s="2">
         <v>119</v>
@@ -35766,7 +35766,7 @@
         <v>78</v>
       </c>
       <c r="AM279" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN279" t="s" s="2">
         <v>78</v>
@@ -35871,7 +35871,7 @@
         <v>80</v>
       </c>
       <c r="AI280" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ280" t="s" s="2">
         <v>102</v>
@@ -35990,7 +35990,7 @@
         <v>80</v>
       </c>
       <c r="AI281" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ281" t="s" s="2">
         <v>102</v>
@@ -36109,7 +36109,7 @@
         <v>80</v>
       </c>
       <c r="AI282" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ282" t="s" s="2">
         <v>102</v>
@@ -36228,7 +36228,7 @@
         <v>90</v>
       </c>
       <c r="AI283" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ283" t="s" s="2">
         <v>102</v>
@@ -36577,7 +36577,7 @@
         <v>80</v>
       </c>
       <c r="AI286" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ286" t="s" s="2">
         <v>119</v>
@@ -36589,7 +36589,7 @@
         <v>78</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -842,8 +842,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -5956,7 +5956,7 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>119</v>
@@ -5968,7 +5968,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -6073,7 +6073,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>119</v>
@@ -6303,7 +6303,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>119</v>
@@ -6533,7 +6533,7 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
@@ -6650,7 +6650,7 @@
         <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>119</v>
@@ -6880,7 +6880,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>119</v>
@@ -7110,7 +7110,7 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
@@ -7227,7 +7227,7 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>119</v>
@@ -7457,7 +7457,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>119</v>
@@ -7689,7 +7689,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -7921,7 +7921,7 @@
         <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>119</v>
@@ -7933,7 +7933,7 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -8274,7 +8274,7 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>119</v>
@@ -8504,7 +8504,7 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>119</v>
@@ -8734,7 +8734,7 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -8851,7 +8851,7 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>119</v>
@@ -9081,7 +9081,7 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>119</v>
@@ -9311,7 +9311,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -9428,7 +9428,7 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>119</v>
@@ -9658,7 +9658,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -9890,7 +9890,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -10122,7 +10122,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -10471,7 +10471,7 @@
         <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>119</v>
@@ -10483,7 +10483,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10588,7 +10588,7 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>119</v>
@@ -10818,7 +10818,7 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>119</v>
@@ -11048,7 +11048,7 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>102</v>
@@ -11165,7 +11165,7 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>119</v>
@@ -11395,7 +11395,7 @@
         <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>119</v>
@@ -11627,7 +11627,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11859,7 +11859,7 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>119</v>
@@ -11871,7 +11871,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -12212,7 +12212,7 @@
         <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>119</v>
@@ -12442,7 +12442,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>119</v>
@@ -12672,7 +12672,7 @@
         <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>102</v>
@@ -12789,7 +12789,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>119</v>
@@ -13019,7 +13019,7 @@
         <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>119</v>
@@ -13249,7 +13249,7 @@
         <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>102</v>
@@ -13481,7 +13481,7 @@
         <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>102</v>
@@ -13947,7 +13947,7 @@
         <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>119</v>
@@ -13959,7 +13959,7 @@
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -14064,7 +14064,7 @@
         <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>119</v>
@@ -14294,7 +14294,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>119</v>
@@ -14526,7 +14526,7 @@
         <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>102</v>
@@ -14643,7 +14643,7 @@
         <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>119</v>
@@ -14873,7 +14873,7 @@
         <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>119</v>
@@ -15105,7 +15105,7 @@
         <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>102</v>
@@ -15222,7 +15222,7 @@
         <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>119</v>
@@ -15452,7 +15452,7 @@
         <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>119</v>
@@ -15684,7 +15684,7 @@
         <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>102</v>
@@ -15801,7 +15801,7 @@
         <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>119</v>
@@ -16031,7 +16031,7 @@
         <v>80</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>119</v>
@@ -16263,7 +16263,7 @@
         <v>90</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>102</v>
@@ -16495,7 +16495,7 @@
         <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>119</v>
@@ -16507,7 +16507,7 @@
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>78</v>
@@ -16848,7 +16848,7 @@
         <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>119</v>
@@ -17078,7 +17078,7 @@
         <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>119</v>
@@ -17310,7 +17310,7 @@
         <v>90</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>102</v>
@@ -17427,7 +17427,7 @@
         <v>80</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>119</v>
@@ -17657,7 +17657,7 @@
         <v>80</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>119</v>
@@ -17889,7 +17889,7 @@
         <v>90</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>102</v>
@@ -18006,7 +18006,7 @@
         <v>80</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>119</v>
@@ -18236,7 +18236,7 @@
         <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>119</v>
@@ -18468,7 +18468,7 @@
         <v>90</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>102</v>
@@ -18700,7 +18700,7 @@
         <v>90</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>102</v>
@@ -29002,7 +29002,7 @@
         <v>80</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>119</v>
@@ -29014,7 +29014,7 @@
         <v>78</v>
       </c>
       <c r="AM221" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN221" t="s" s="2">
         <v>78</v>
@@ -29119,7 +29119,7 @@
         <v>80</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>119</v>
@@ -29349,7 +29349,7 @@
         <v>80</v>
       </c>
       <c r="AI224" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ224" t="s" s="2">
         <v>119</v>
@@ -29579,7 +29579,7 @@
         <v>90</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ226" t="s" s="2">
         <v>102</v>
@@ -29696,7 +29696,7 @@
         <v>80</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ227" t="s" s="2">
         <v>119</v>
@@ -29926,7 +29926,7 @@
         <v>80</v>
       </c>
       <c r="AI229" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ229" t="s" s="2">
         <v>119</v>
@@ -30156,7 +30156,7 @@
         <v>90</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>102</v>
@@ -30273,7 +30273,7 @@
         <v>80</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>119</v>
@@ -30503,7 +30503,7 @@
         <v>80</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ234" t="s" s="2">
         <v>119</v>
@@ -30733,7 +30733,7 @@
         <v>90</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>102</v>
@@ -30965,7 +30965,7 @@
         <v>90</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>102</v>
@@ -31546,7 +31546,7 @@
         <v>80</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ243" t="s" s="2">
         <v>119</v>
@@ -31558,7 +31558,7 @@
         <v>78</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN243" t="s" s="2">
         <v>78</v>
@@ -31663,7 +31663,7 @@
         <v>80</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ244" t="s" s="2">
         <v>102</v>
@@ -31782,7 +31782,7 @@
         <v>80</v>
       </c>
       <c r="AI245" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ245" t="s" s="2">
         <v>102</v>
@@ -31901,7 +31901,7 @@
         <v>80</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ246" t="s" s="2">
         <v>102</v>
@@ -32020,7 +32020,7 @@
         <v>90</v>
       </c>
       <c r="AI247" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ247" t="s" s="2">
         <v>102</v>
@@ -32369,7 +32369,7 @@
         <v>80</v>
       </c>
       <c r="AI250" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ250" t="s" s="2">
         <v>119</v>
@@ -32381,7 +32381,7 @@
         <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -33650,7 +33650,7 @@
         <v>80</v>
       </c>
       <c r="AI261" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ261" t="s" s="2">
         <v>119</v>
@@ -33662,7 +33662,7 @@
         <v>78</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>78</v>
@@ -33767,7 +33767,7 @@
         <v>80</v>
       </c>
       <c r="AI262" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ262" t="s" s="2">
         <v>102</v>
@@ -33886,7 +33886,7 @@
         <v>80</v>
       </c>
       <c r="AI263" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ263" t="s" s="2">
         <v>102</v>
@@ -34005,7 +34005,7 @@
         <v>80</v>
       </c>
       <c r="AI264" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ264" t="s" s="2">
         <v>102</v>
@@ -34124,7 +34124,7 @@
         <v>90</v>
       </c>
       <c r="AI265" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ265" t="s" s="2">
         <v>102</v>
@@ -34473,7 +34473,7 @@
         <v>80</v>
       </c>
       <c r="AI268" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ268" t="s" s="2">
         <v>119</v>
@@ -34485,7 +34485,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -35754,7 +35754,7 @@
         <v>80</v>
       </c>
       <c r="AI279" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ279" t="s" s="2">
         <v>119</v>
@@ -35766,7 +35766,7 @@
         <v>78</v>
       </c>
       <c r="AM279" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN279" t="s" s="2">
         <v>78</v>
@@ -35871,7 +35871,7 @@
         <v>80</v>
       </c>
       <c r="AI280" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ280" t="s" s="2">
         <v>102</v>
@@ -35990,7 +35990,7 @@
         <v>80</v>
       </c>
       <c r="AI281" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ281" t="s" s="2">
         <v>102</v>
@@ -36109,7 +36109,7 @@
         <v>80</v>
       </c>
       <c r="AI282" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ282" t="s" s="2">
         <v>102</v>
@@ -36228,7 +36228,7 @@
         <v>90</v>
       </c>
       <c r="AI283" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ283" t="s" s="2">
         <v>102</v>
@@ -36577,7 +36577,7 @@
         <v>80</v>
       </c>
       <c r="AI286" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ286" t="s" s="2">
         <v>119</v>
@@ -36589,7 +36589,7 @@
         <v>78</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10691" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10691" uniqueCount="940">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -842,8 +842,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -1725,9 +1725,13 @@
     <t>Practitioner.identifier:idNatPs.type</t>
   </si>
   <si>
+    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
+Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+  </si>
+  <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="IDNPS"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1787,7 +1791,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="RPPS"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1796,7 +1800,7 @@
     <t>Practitioner.identifier:rpps.system</t>
   </si>
   <si>
-    <t>http://rpps.esante.gouv.fr</t>
+    <t>https://rpps.esante.gouv.fr</t>
   </si>
   <si>
     <t>Practitioner.identifier:rpps.value</t>
@@ -1831,7 +1835,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="ADELI"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1840,7 +1844,7 @@
     <t>Practitioner.identifier:adeli.system</t>
   </si>
   <si>
-    <t>http://adeli.esante.gouv.fr</t>
+    <t>https://adeli.esante.gouv.fr</t>
   </si>
   <si>
     <t>Practitioner.identifier:adeli.value</t>
@@ -5956,7 +5960,7 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>119</v>
@@ -5968,7 +5972,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -6073,7 +6077,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>119</v>
@@ -6303,7 +6307,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>119</v>
@@ -6533,7 +6537,7 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
@@ -6650,7 +6654,7 @@
         <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>119</v>
@@ -6880,7 +6884,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>119</v>
@@ -7110,7 +7114,7 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
@@ -7227,7 +7231,7 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>119</v>
@@ -7457,7 +7461,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>119</v>
@@ -7689,7 +7693,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -7921,7 +7925,7 @@
         <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>119</v>
@@ -7933,7 +7937,7 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -8274,7 +8278,7 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>119</v>
@@ -8504,7 +8508,7 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>119</v>
@@ -8734,7 +8738,7 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -8851,7 +8855,7 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>119</v>
@@ -9081,7 +9085,7 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>119</v>
@@ -9311,7 +9315,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -9428,7 +9432,7 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>119</v>
@@ -9658,7 +9662,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -9890,7 +9894,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -10122,7 +10126,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -10471,7 +10475,7 @@
         <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>119</v>
@@ -10483,7 +10487,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10588,7 +10592,7 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>119</v>
@@ -10818,7 +10822,7 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>119</v>
@@ -11048,7 +11052,7 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>102</v>
@@ -11165,7 +11169,7 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>119</v>
@@ -11395,7 +11399,7 @@
         <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>119</v>
@@ -11627,7 +11631,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11859,7 +11863,7 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>119</v>
@@ -11871,7 +11875,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -12212,7 +12216,7 @@
         <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>119</v>
@@ -12442,7 +12446,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>119</v>
@@ -12672,7 +12676,7 @@
         <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>102</v>
@@ -12789,7 +12793,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>119</v>
@@ -13019,7 +13023,7 @@
         <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>119</v>
@@ -13249,7 +13253,7 @@
         <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>102</v>
@@ -13481,7 +13485,7 @@
         <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>102</v>
@@ -13947,7 +13951,7 @@
         <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>119</v>
@@ -13959,7 +13963,7 @@
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -14064,7 +14068,7 @@
         <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>119</v>
@@ -14294,7 +14298,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>119</v>
@@ -14526,7 +14530,7 @@
         <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>102</v>
@@ -14643,7 +14647,7 @@
         <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>119</v>
@@ -14873,7 +14877,7 @@
         <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>119</v>
@@ -15105,7 +15109,7 @@
         <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>102</v>
@@ -15222,7 +15226,7 @@
         <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>119</v>
@@ -15452,7 +15456,7 @@
         <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>119</v>
@@ -15684,7 +15688,7 @@
         <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>102</v>
@@ -15801,7 +15805,7 @@
         <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>119</v>
@@ -16031,7 +16035,7 @@
         <v>80</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>119</v>
@@ -16263,7 +16267,7 @@
         <v>90</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>102</v>
@@ -16495,7 +16499,7 @@
         <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>119</v>
@@ -16507,7 +16511,7 @@
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>78</v>
@@ -16848,7 +16852,7 @@
         <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>119</v>
@@ -17078,7 +17082,7 @@
         <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>119</v>
@@ -17310,7 +17314,7 @@
         <v>90</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>102</v>
@@ -17427,7 +17431,7 @@
         <v>80</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>119</v>
@@ -17657,7 +17661,7 @@
         <v>80</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>119</v>
@@ -17889,7 +17893,7 @@
         <v>90</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>102</v>
@@ -18006,7 +18010,7 @@
         <v>80</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>119</v>
@@ -18236,7 +18240,7 @@
         <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>119</v>
@@ -18468,7 +18472,7 @@
         <v>90</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>102</v>
@@ -18700,7 +18704,7 @@
         <v>90</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>102</v>
@@ -21685,7 +21689,7 @@
         <v>233</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>444</v>
+        <v>551</v>
       </c>
       <c r="M159" t="s" s="2">
         <v>445</v>
@@ -21704,7 +21708,7 @@
         <v>78</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>78</v>
@@ -21722,10 +21726,10 @@
         <v>158</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>78</v>
@@ -21775,7 +21779,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>509</v>
@@ -21807,7 +21811,7 @@
         <v>510</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>512</v>
@@ -21823,7 +21827,7 @@
         <v>78</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>514</v>
@@ -21894,7 +21898,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>519</v>
@@ -21923,7 +21927,7 @@
         <v>104</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M161" t="s" s="2">
         <v>521</v>
@@ -22011,7 +22015,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>528</v>
@@ -22126,7 +22130,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>535</v>
@@ -22243,13 +22247,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>421</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
@@ -22274,7 +22278,7 @@
         <v>422</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M164" t="s" s="2">
         <v>424</v>
@@ -22362,7 +22366,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>432</v>
@@ -22477,7 +22481,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>433</v>
@@ -22594,7 +22598,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>434</v>
@@ -22713,7 +22717,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>443</v>
@@ -22742,7 +22746,7 @@
         <v>233</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M168" t="s" s="2">
         <v>445</v>
@@ -22761,7 +22765,7 @@
         <v>78</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>78</v>
@@ -22779,10 +22783,10 @@
         <v>158</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>78</v>
@@ -22832,7 +22836,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>509</v>
@@ -22864,7 +22868,7 @@
         <v>510</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>512</v>
@@ -22880,7 +22884,7 @@
         <v>78</v>
       </c>
       <c r="S169" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="T169" t="s" s="2">
         <v>514</v>
@@ -22951,7 +22955,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>519</v>
@@ -23068,7 +23072,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>528</v>
@@ -23183,7 +23187,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>535</v>
@@ -23300,13 +23304,13 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>421</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>78</v>
@@ -23331,7 +23335,7 @@
         <v>422</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>424</v>
@@ -23419,7 +23423,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>432</v>
@@ -23534,7 +23538,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>433</v>
@@ -23651,7 +23655,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>434</v>
@@ -23770,7 +23774,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>443</v>
@@ -23799,7 +23803,7 @@
         <v>233</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>445</v>
@@ -23818,7 +23822,7 @@
         <v>78</v>
       </c>
       <c r="S177" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="T177" t="s" s="2">
         <v>78</v>
@@ -23836,10 +23840,10 @@
         <v>158</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>78</v>
@@ -23889,7 +23893,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>509</v>
@@ -23921,7 +23925,7 @@
         <v>510</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N178" t="s" s="2">
         <v>512</v>
@@ -23937,7 +23941,7 @@
         <v>78</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>514</v>
@@ -24008,7 +24012,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>519</v>
@@ -24125,7 +24129,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>528</v>
@@ -24240,7 +24244,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>535</v>
@@ -24357,10 +24361,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24386,67 +24390,67 @@
         <v>297</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="P182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q182" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="R182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF182" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="P182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q182" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="R182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF182" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -24467,21 +24471,21 @@
         <v>78</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24504,19 +24508,19 @@
         <v>78</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>78</v>
@@ -24565,7 +24569,7 @@
         <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24583,13 +24587,13 @@
         <v>78</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>78</v>
@@ -24597,10 +24601,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24712,10 +24716,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24829,13 +24833,13 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B186" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="B186" t="s" s="2">
-        <v>606</v>
-      </c>
       <c r="C186" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D186" t="s" s="2">
         <v>78</v>
@@ -24857,13 +24861,13 @@
         <v>78</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -24946,10 +24950,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24975,16 +24979,16 @@
         <v>176</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -25013,7 +25017,7 @@
       </c>
       <c r="Y187" s="2"/>
       <c r="Z187" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>78</v>
@@ -25031,7 +25035,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -25049,13 +25053,13 @@
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>78</v>
@@ -25063,10 +25067,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25092,16 +25096,16 @@
         <v>104</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -25150,7 +25154,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -25168,10 +25172,10 @@
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>78</v>
@@ -25182,14 +25186,14 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
@@ -25211,13 +25215,13 @@
         <v>104</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -25267,7 +25271,7 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -25285,13 +25289,13 @@
         <v>78</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>78</v>
@@ -25299,14 +25303,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -25328,13 +25332,13 @@
         <v>104</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
@@ -25384,7 +25388,7 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
@@ -25402,13 +25406,13 @@
         <v>78</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>78</v>
@@ -25416,10 +25420,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25445,10 +25449,10 @@
         <v>104</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -25478,10 +25482,10 @@
         <v>158</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>78</v>
@@ -25499,7 +25503,7 @@
         <v>78</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -25517,13 +25521,13 @@
         <v>78</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>78</v>
@@ -25531,10 +25535,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25560,10 +25564,10 @@
         <v>104</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -25593,10 +25597,10 @@
         <v>158</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>78</v>
@@ -25614,7 +25618,7 @@
         <v>78</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
@@ -25632,10 +25636,10 @@
         <v>78</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>78</v>
@@ -25646,10 +25650,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25675,14 +25679,14 @@
         <v>253</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>78</v>
@@ -25731,7 +25735,7 @@
         <v>78</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -25749,10 +25753,10 @@
         <v>78</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>534</v>
@@ -25763,10 +25767,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25789,19 +25793,19 @@
         <v>78</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>78</v>
@@ -25838,7 +25842,7 @@
         <v>78</v>
       </c>
       <c r="AB194" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AC194" s="2"/>
       <c r="AD194" t="s" s="2">
@@ -25848,7 +25852,7 @@
         <v>117</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
@@ -25860,19 +25864,19 @@
         <v>209</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AK194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>78</v>
@@ -25880,10 +25884,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25995,10 +25999,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26112,13 +26116,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B197" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="B197" t="s" s="2">
-        <v>684</v>
-      </c>
       <c r="C197" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>78</v>
@@ -26140,13 +26144,13 @@
         <v>78</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -26229,10 +26233,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26258,10 +26262,10 @@
         <v>176</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -26291,10 +26295,10 @@
         <v>236</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>78</v>
@@ -26312,7 +26316,7 @@
         <v>78</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -26321,7 +26325,7 @@
         <v>90</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AJ198" t="s" s="2">
         <v>102</v>
@@ -26330,13 +26334,13 @@
         <v>78</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AM198" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>78</v>
@@ -26344,10 +26348,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26373,16 +26377,16 @@
         <v>104</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>78</v>
@@ -26431,7 +26435,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26449,10 +26453,10 @@
         <v>78</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AM199" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AN199" t="s" s="2">
         <v>527</v>
@@ -26463,10 +26467,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26492,16 +26496,16 @@
         <v>176</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>78</v>
@@ -26529,10 +26533,10 @@
         <v>236</v>
       </c>
       <c r="Y200" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="Z200" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>78</v>
@@ -26550,7 +26554,7 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26568,13 +26572,13 @@
         <v>78</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>78</v>
@@ -26582,10 +26586,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26608,16 +26612,16 @@
         <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -26667,7 +26671,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -26699,10 +26703,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26728,10 +26732,10 @@
         <v>253</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -26782,7 +26786,7 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
@@ -26803,7 +26807,7 @@
         <v>199</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>534</v>
@@ -26814,13 +26818,13 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D203" t="s" s="2">
         <v>78</v>
@@ -26842,19 +26846,19 @@
         <v>78</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>78</v>
@@ -26903,7 +26907,7 @@
         <v>78</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -26915,19 +26919,19 @@
         <v>209</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AK203" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AM203" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>78</v>
@@ -26935,10 +26939,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26961,19 +26965,19 @@
         <v>78</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>78</v>
@@ -27022,7 +27026,7 @@
         <v>78</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
@@ -27040,13 +27044,13 @@
         <v>78</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>78</v>
@@ -27054,10 +27058,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27083,14 +27087,14 @@
         <v>176</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>78</v>
@@ -27118,10 +27122,10 @@
         <v>236</v>
       </c>
       <c r="Y205" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="Z205" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AA205" t="s" s="2">
         <v>78</v>
@@ -27139,7 +27143,7 @@
         <v>78</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
@@ -27157,13 +27161,13 @@
         <v>78</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>78</v>
@@ -27171,10 +27175,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27197,17 +27201,17 @@
         <v>91</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>78</v>
@@ -27256,7 +27260,7 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
@@ -27274,13 +27278,13 @@
         <v>78</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>78</v>
@@ -27288,10 +27292,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27317,14 +27321,14 @@
         <v>412</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>78</v>
@@ -27373,7 +27377,7 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
@@ -27394,10 +27398,10 @@
         <v>78</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>78</v>
@@ -27405,10 +27409,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27431,13 +27435,13 @@
         <v>78</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -27476,7 +27480,7 @@
         <v>78</v>
       </c>
       <c r="AB208" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AC208" s="2"/>
       <c r="AD208" t="s" s="2">
@@ -27486,7 +27490,7 @@
         <v>117</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27504,13 +27508,13 @@
         <v>78</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>78</v>
@@ -27518,10 +27522,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27633,10 +27637,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27750,14 +27754,14 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
@@ -27779,10 +27783,10 @@
         <v>111</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N211" t="s" s="2">
         <v>114</v>
@@ -27837,7 +27841,7 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -27869,10 +27873,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -27898,14 +27902,14 @@
         <v>422</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
@@ -27954,7 +27958,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -27975,7 +27979,7 @@
         <v>78</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AN212" t="s" s="2">
         <v>78</v>
@@ -27986,10 +27990,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28015,10 +28019,10 @@
         <v>233</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -28049,7 +28053,7 @@
       </c>
       <c r="Y213" s="2"/>
       <c r="Z213" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>78</v>
@@ -28067,7 +28071,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>90</v>
@@ -28088,10 +28092,10 @@
         <v>78</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>78</v>
@@ -28099,10 +28103,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28128,14 +28132,14 @@
         <v>253</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28184,7 +28188,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28205,10 +28209,10 @@
         <v>78</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28216,10 +28220,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28245,10 +28249,10 @@
         <v>536</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -28299,7 +28303,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28320,7 +28324,7 @@
         <v>78</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN215" t="s" s="2">
         <v>78</v>
@@ -28331,13 +28335,13 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D216" t="s" s="2">
         <v>78</v>
@@ -28359,13 +28363,13 @@
         <v>78</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -28416,7 +28420,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28434,13 +28438,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28448,10 +28452,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28563,10 +28567,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28676,13 +28680,13 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D219" t="s" s="2">
         <v>78</v>
@@ -28704,13 +28708,13 @@
         <v>78</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -28793,10 +28797,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28908,10 +28912,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29002,7 +29006,7 @@
         <v>80</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>119</v>
@@ -29014,7 +29018,7 @@
         <v>78</v>
       </c>
       <c r="AM221" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN221" t="s" s="2">
         <v>78</v>
@@ -29025,13 +29029,13 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B222" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="B222" t="s" s="2">
-        <v>812</v>
-      </c>
       <c r="C222" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>78</v>
@@ -29119,7 +29123,7 @@
         <v>80</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>119</v>
@@ -29142,10 +29146,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29257,10 +29261,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29349,7 +29353,7 @@
         <v>80</v>
       </c>
       <c r="AI224" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ224" t="s" s="2">
         <v>119</v>
@@ -29372,10 +29376,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29415,7 +29419,7 @@
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="S225" t="s" s="2">
         <v>78</v>
@@ -29489,10 +29493,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29552,7 +29556,7 @@
       </c>
       <c r="Y226" s="2"/>
       <c r="Z226" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>78</v>
@@ -29579,7 +29583,7 @@
         <v>90</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ226" t="s" s="2">
         <v>102</v>
@@ -29602,13 +29606,13 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D227" t="s" s="2">
         <v>78</v>
@@ -29696,7 +29700,7 @@
         <v>80</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ227" t="s" s="2">
         <v>119</v>
@@ -29719,10 +29723,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29834,10 +29838,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -29926,7 +29930,7 @@
         <v>80</v>
       </c>
       <c r="AI229" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ229" t="s" s="2">
         <v>119</v>
@@ -29949,10 +29953,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -29992,7 +29996,7 @@
       </c>
       <c r="Q230" s="2"/>
       <c r="R230" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="S230" t="s" s="2">
         <v>78</v>
@@ -30066,10 +30070,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30129,7 +30133,7 @@
       </c>
       <c r="Y231" s="2"/>
       <c r="Z231" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>78</v>
@@ -30156,7 +30160,7 @@
         <v>90</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>102</v>
@@ -30179,13 +30183,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30273,7 +30277,7 @@
         <v>80</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>119</v>
@@ -30296,10 +30300,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30411,10 +30415,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30503,7 +30507,7 @@
         <v>80</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ234" t="s" s="2">
         <v>119</v>
@@ -30526,10 +30530,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30569,7 +30573,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>78</v>
@@ -30643,10 +30647,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30706,7 +30710,7 @@
       </c>
       <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>78</v>
@@ -30733,7 +30737,7 @@
         <v>90</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>102</v>
@@ -30756,10 +30760,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -30799,7 +30803,7 @@
       </c>
       <c r="Q237" s="2"/>
       <c r="R237" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="S237" t="s" s="2">
         <v>78</v>
@@ -30873,10 +30877,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -30965,7 +30969,7 @@
         <v>90</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>102</v>
@@ -30988,14 +30992,14 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
@@ -31017,10 +31021,10 @@
         <v>111</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N239" t="s" s="2">
         <v>114</v>
@@ -31075,7 +31079,7 @@
         <v>78</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>79</v>
@@ -31107,10 +31111,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31136,14 +31140,14 @@
         <v>422</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>78</v>
@@ -31192,7 +31196,7 @@
         <v>78</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>79</v>
@@ -31213,7 +31217,7 @@
         <v>78</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AN240" t="s" s="2">
         <v>78</v>
@@ -31224,10 +31228,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31253,10 +31257,10 @@
         <v>233</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -31287,7 +31291,7 @@
       </c>
       <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>78</v>
@@ -31305,7 +31309,7 @@
         <v>78</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>90</v>
@@ -31326,10 +31330,10 @@
         <v>78</v>
       </c>
       <c r="AM241" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN241" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AO241" t="s" s="2">
         <v>78</v>
@@ -31337,10 +31341,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -31452,10 +31456,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31546,7 +31550,7 @@
         <v>80</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ243" t="s" s="2">
         <v>119</v>
@@ -31558,7 +31562,7 @@
         <v>78</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN243" t="s" s="2">
         <v>78</v>
@@ -31569,10 +31573,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31644,14 +31648,14 @@
         <v>78</v>
       </c>
       <c r="AB244" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AC244" s="2"/>
       <c r="AD244" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE244" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AF244" t="s" s="2">
         <v>458</v>
@@ -31663,7 +31667,7 @@
         <v>80</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ244" t="s" s="2">
         <v>102</v>
@@ -31686,13 +31690,13 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D245" t="s" s="2">
         <v>78</v>
@@ -31755,7 +31759,7 @@
       </c>
       <c r="Y245" s="2"/>
       <c r="Z245" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>78</v>
@@ -31782,7 +31786,7 @@
         <v>80</v>
       </c>
       <c r="AI245" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ245" t="s" s="2">
         <v>102</v>
@@ -31805,13 +31809,13 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D246" t="s" s="2">
         <v>78</v>
@@ -31874,7 +31878,7 @@
       </c>
       <c r="Y246" s="2"/>
       <c r="Z246" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>78</v>
@@ -31901,7 +31905,7 @@
         <v>80</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ246" t="s" s="2">
         <v>102</v>
@@ -31924,10 +31928,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32020,7 +32024,7 @@
         <v>90</v>
       </c>
       <c r="AI247" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ247" t="s" s="2">
         <v>102</v>
@@ -32043,10 +32047,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32072,14 +32076,14 @@
         <v>253</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>78</v>
@@ -32128,7 +32132,7 @@
         <v>78</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>79</v>
@@ -32149,10 +32153,10 @@
         <v>78</v>
       </c>
       <c r="AM248" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AN248" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AO248" t="s" s="2">
         <v>78</v>
@@ -32160,10 +32164,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32275,10 +32279,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32369,7 +32373,7 @@
         <v>80</v>
       </c>
       <c r="AI250" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ250" t="s" s="2">
         <v>119</v>
@@ -32381,7 +32385,7 @@
         <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -32392,10 +32396,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32421,7 +32425,7 @@
         <v>260</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M251" t="s" s="2">
         <v>262</v>
@@ -32509,10 +32513,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32538,7 +32542,7 @@
         <v>260</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M252" t="s" s="2">
         <v>271</v>
@@ -32628,10 +32632,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32654,13 +32658,13 @@
         <v>78</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
@@ -32711,7 +32715,7 @@
         <v>78</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>79</v>
@@ -32732,7 +32736,7 @@
         <v>78</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>78</v>
@@ -32743,13 +32747,13 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D254" t="s" s="2">
         <v>78</v>
@@ -32771,13 +32775,13 @@
         <v>78</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
@@ -32828,7 +32832,7 @@
         <v>78</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>79</v>
@@ -32846,13 +32850,13 @@
         <v>78</v>
       </c>
       <c r="AL254" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AM254" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN254" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO254" t="s" s="2">
         <v>78</v>
@@ -32860,10 +32864,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -32975,10 +32979,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -33092,14 +33096,14 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
@@ -33121,10 +33125,10 @@
         <v>111</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N257" t="s" s="2">
         <v>114</v>
@@ -33179,7 +33183,7 @@
         <v>78</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>79</v>
@@ -33211,10 +33215,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33240,14 +33244,14 @@
         <v>422</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>78</v>
@@ -33296,7 +33300,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33317,7 +33321,7 @@
         <v>78</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AN258" t="s" s="2">
         <v>78</v>
@@ -33328,10 +33332,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33357,10 +33361,10 @@
         <v>233</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N259" s="2"/>
       <c r="O259" s="2"/>
@@ -33391,7 +33395,7 @@
       </c>
       <c r="Y259" s="2"/>
       <c r="Z259" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA259" t="s" s="2">
         <v>78</v>
@@ -33409,7 +33413,7 @@
         <v>78</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>90</v>
@@ -33430,10 +33434,10 @@
         <v>78</v>
       </c>
       <c r="AM259" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN259" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AO259" t="s" s="2">
         <v>78</v>
@@ -33441,10 +33445,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33556,10 +33560,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33650,7 +33654,7 @@
         <v>80</v>
       </c>
       <c r="AI261" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ261" t="s" s="2">
         <v>119</v>
@@ -33662,7 +33666,7 @@
         <v>78</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>78</v>
@@ -33673,10 +33677,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33748,14 +33752,14 @@
         <v>78</v>
       </c>
       <c r="AB262" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AC262" s="2"/>
       <c r="AD262" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE262" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AF262" t="s" s="2">
         <v>458</v>
@@ -33767,7 +33771,7 @@
         <v>80</v>
       </c>
       <c r="AI262" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ262" t="s" s="2">
         <v>102</v>
@@ -33790,13 +33794,13 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D263" t="s" s="2">
         <v>78</v>
@@ -33821,7 +33825,7 @@
         <v>154</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="M263" t="s" s="2">
         <v>455</v>
@@ -33859,7 +33863,7 @@
       </c>
       <c r="Y263" s="2"/>
       <c r="Z263" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AA263" t="s" s="2">
         <v>78</v>
@@ -33886,7 +33890,7 @@
         <v>80</v>
       </c>
       <c r="AI263" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ263" t="s" s="2">
         <v>102</v>
@@ -33909,10 +33913,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C264" t="s" s="2">
         <v>337</v>
@@ -33940,7 +33944,7 @@
         <v>154</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M264" t="s" s="2">
         <v>455</v>
@@ -34005,7 +34009,7 @@
         <v>80</v>
       </c>
       <c r="AI264" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ264" t="s" s="2">
         <v>102</v>
@@ -34028,10 +34032,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34124,7 +34128,7 @@
         <v>90</v>
       </c>
       <c r="AI265" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ265" t="s" s="2">
         <v>102</v>
@@ -34147,10 +34151,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34176,14 +34180,14 @@
         <v>253</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N266" s="2"/>
       <c r="O266" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>78</v>
@@ -34232,7 +34236,7 @@
         <v>78</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>79</v>
@@ -34253,10 +34257,10 @@
         <v>78</v>
       </c>
       <c r="AM266" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AN266" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AO266" t="s" s="2">
         <v>78</v>
@@ -34264,10 +34268,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -34379,10 +34383,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34473,7 +34477,7 @@
         <v>80</v>
       </c>
       <c r="AI268" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ268" t="s" s="2">
         <v>119</v>
@@ -34485,7 +34489,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -34496,10 +34500,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34525,7 +34529,7 @@
         <v>260</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="M269" t="s" s="2">
         <v>262</v>
@@ -34613,10 +34617,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34642,7 +34646,7 @@
         <v>260</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M270" t="s" s="2">
         <v>271</v>
@@ -34732,10 +34736,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34761,10 +34765,10 @@
         <v>536</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N271" s="2"/>
       <c r="O271" s="2"/>
@@ -34815,7 +34819,7 @@
         <v>78</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>79</v>
@@ -34836,7 +34840,7 @@
         <v>78</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN271" t="s" s="2">
         <v>78</v>
@@ -34847,13 +34851,13 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D272" t="s" s="2">
         <v>78</v>
@@ -34875,13 +34879,13 @@
         <v>78</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N272" s="2"/>
       <c r="O272" s="2"/>
@@ -34932,7 +34936,7 @@
         <v>78</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>79</v>
@@ -34950,13 +34954,13 @@
         <v>78</v>
       </c>
       <c r="AL272" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AM272" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN272" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AO272" t="s" s="2">
         <v>78</v>
@@ -34964,10 +34968,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -35079,10 +35083,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -35196,14 +35200,14 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E275" s="2"/>
       <c r="F275" t="s" s="2">
@@ -35225,10 +35229,10 @@
         <v>111</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N275" t="s" s="2">
         <v>114</v>
@@ -35283,7 +35287,7 @@
         <v>78</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>79</v>
@@ -35315,10 +35319,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35344,14 +35348,14 @@
         <v>422</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>78</v>
@@ -35400,7 +35404,7 @@
         <v>78</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>79</v>
@@ -35421,7 +35425,7 @@
         <v>78</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AN276" t="s" s="2">
         <v>78</v>
@@ -35432,10 +35436,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35461,10 +35465,10 @@
         <v>233</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N277" s="2"/>
       <c r="O277" s="2"/>
@@ -35495,7 +35499,7 @@
       </c>
       <c r="Y277" s="2"/>
       <c r="Z277" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA277" t="s" s="2">
         <v>78</v>
@@ -35513,7 +35517,7 @@
         <v>78</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>90</v>
@@ -35528,16 +35532,16 @@
         <v>102</v>
       </c>
       <c r="AK277" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="AL277" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM277" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN277" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AO277" t="s" s="2">
         <v>78</v>
@@ -35545,10 +35549,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35660,10 +35664,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35754,7 +35758,7 @@
         <v>80</v>
       </c>
       <c r="AI279" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ279" t="s" s="2">
         <v>119</v>
@@ -35766,7 +35770,7 @@
         <v>78</v>
       </c>
       <c r="AM279" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN279" t="s" s="2">
         <v>78</v>
@@ -35777,10 +35781,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35852,7 +35856,7 @@
         <v>78</v>
       </c>
       <c r="AB280" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AC280" s="2"/>
       <c r="AD280" t="s" s="2">
@@ -35871,7 +35875,7 @@
         <v>80</v>
       </c>
       <c r="AI280" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ280" t="s" s="2">
         <v>102</v>
@@ -35894,13 +35898,13 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D281" t="s" s="2">
         <v>78</v>
@@ -35925,7 +35929,7 @@
         <v>154</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="M281" t="s" s="2">
         <v>455</v>
@@ -35963,7 +35967,7 @@
       </c>
       <c r="Y281" s="2"/>
       <c r="Z281" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="AA281" t="s" s="2">
         <v>78</v>
@@ -35990,7 +35994,7 @@
         <v>80</v>
       </c>
       <c r="AI281" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ281" t="s" s="2">
         <v>102</v>
@@ -36013,13 +36017,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36044,7 +36048,7 @@
         <v>154</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="M282" t="s" s="2">
         <v>455</v>
@@ -36082,7 +36086,7 @@
       </c>
       <c r="Y282" s="2"/>
       <c r="Z282" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="AA282" t="s" s="2">
         <v>78</v>
@@ -36109,7 +36113,7 @@
         <v>80</v>
       </c>
       <c r="AI282" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ282" t="s" s="2">
         <v>102</v>
@@ -36132,10 +36136,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36228,7 +36232,7 @@
         <v>90</v>
       </c>
       <c r="AI283" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ283" t="s" s="2">
         <v>102</v>
@@ -36251,10 +36255,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36280,14 +36284,14 @@
         <v>253</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="P284" t="s" s="2">
         <v>78</v>
@@ -36336,7 +36340,7 @@
         <v>78</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>79</v>
@@ -36357,10 +36361,10 @@
         <v>78</v>
       </c>
       <c r="AM284" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AN284" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AO284" t="s" s="2">
         <v>78</v>
@@ -36368,10 +36372,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -36483,10 +36487,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36577,7 +36581,7 @@
         <v>80</v>
       </c>
       <c r="AI286" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ286" t="s" s="2">
         <v>119</v>
@@ -36589,7 +36593,7 @@
         <v>78</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>78</v>
@@ -36600,10 +36604,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36629,7 +36633,7 @@
         <v>260</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="M287" t="s" s="2">
         <v>262</v>
@@ -36700,7 +36704,7 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>266</v>
@@ -36717,10 +36721,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36746,7 +36750,7 @@
         <v>260</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M288" t="s" s="2">
         <v>271</v>
@@ -36819,7 +36823,7 @@
         <v>102</v>
       </c>
       <c r="AK288" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AL288" t="s" s="2">
         <v>275</v>
@@ -36836,10 +36840,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -36865,10 +36869,10 @@
         <v>536</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="2"/>
@@ -36919,7 +36923,7 @@
         <v>78</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>79</v>
@@ -36940,7 +36944,7 @@
         <v>78</v>
       </c>
       <c r="AM289" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN289" t="s" s="2">
         <v>78</v>
@@ -36951,10 +36955,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -36977,19 +36981,19 @@
         <v>78</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N290" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="O290" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="P290" t="s" s="2">
         <v>78</v>
@@ -37018,7 +37022,7 @@
       </c>
       <c r="Y290" s="2"/>
       <c r="Z290" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AA290" t="s" s="2">
         <v>78</v>
@@ -37036,7 +37040,7 @@
         <v>78</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>79</v>
@@ -37054,10 +37058,10 @@
         <v>78</v>
       </c>
       <c r="AL290" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="AM290" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AN290" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10691" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10691" uniqueCount="939">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1400,7 +1400,7 @@
   </si>
   <si>
     <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1723,10 +1723,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.type</t>
-  </si>
-  <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -21689,7 +21685,7 @@
         <v>233</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>551</v>
+        <v>444</v>
       </c>
       <c r="M159" t="s" s="2">
         <v>445</v>
@@ -21708,7 +21704,7 @@
         <v>78</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>78</v>
@@ -21726,10 +21722,10 @@
         <v>158</v>
       </c>
       <c r="Y159" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="Z159" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>78</v>
@@ -21779,7 +21775,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>509</v>
@@ -21811,7 +21807,7 @@
         <v>510</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>512</v>
@@ -21827,7 +21823,7 @@
         <v>78</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>514</v>
@@ -21898,7 +21894,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>519</v>
@@ -21927,7 +21923,7 @@
         <v>104</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="M161" t="s" s="2">
         <v>521</v>
@@ -22015,7 +22011,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>528</v>
@@ -22130,7 +22126,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>535</v>
@@ -22247,13 +22243,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>421</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
@@ -22278,7 +22274,7 @@
         <v>422</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M164" t="s" s="2">
         <v>424</v>
@@ -22366,7 +22362,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>432</v>
@@ -22481,7 +22477,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>433</v>
@@ -22598,7 +22594,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>434</v>
@@ -22717,7 +22713,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>443</v>
@@ -22746,7 +22742,7 @@
         <v>233</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M168" t="s" s="2">
         <v>445</v>
@@ -22765,7 +22761,7 @@
         <v>78</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>78</v>
@@ -22783,10 +22779,10 @@
         <v>158</v>
       </c>
       <c r="Y168" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="Z168" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="Z168" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>78</v>
@@ -22836,7 +22832,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>509</v>
@@ -22868,7 +22864,7 @@
         <v>510</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>512</v>
@@ -22884,7 +22880,7 @@
         <v>78</v>
       </c>
       <c r="S169" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="T169" t="s" s="2">
         <v>514</v>
@@ -22955,7 +22951,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>519</v>
@@ -23072,7 +23068,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>528</v>
@@ -23187,7 +23183,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>535</v>
@@ -23304,13 +23300,13 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>421</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>78</v>
@@ -23335,7 +23331,7 @@
         <v>422</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="M173" t="s" s="2">
         <v>424</v>
@@ -23423,7 +23419,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>432</v>
@@ -23538,7 +23534,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>433</v>
@@ -23655,7 +23651,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>434</v>
@@ -23774,7 +23770,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>443</v>
@@ -23803,7 +23799,7 @@
         <v>233</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>445</v>
@@ -23822,7 +23818,7 @@
         <v>78</v>
       </c>
       <c r="S177" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="T177" t="s" s="2">
         <v>78</v>
@@ -23840,10 +23836,10 @@
         <v>158</v>
       </c>
       <c r="Y177" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="Z177" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="Z177" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>78</v>
@@ -23893,7 +23889,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>509</v>
@@ -23925,7 +23921,7 @@
         <v>510</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="N178" t="s" s="2">
         <v>512</v>
@@ -23941,7 +23937,7 @@
         <v>78</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>514</v>
@@ -24012,7 +24008,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>519</v>
@@ -24129,7 +24125,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>528</v>
@@ -24244,7 +24240,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>535</v>
@@ -24361,10 +24357,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24390,23 +24386,23 @@
         <v>297</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M182" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="M182" t="s" s="2">
+      <c r="N182" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="N182" t="s" s="2">
+      <c r="O182" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="O182" t="s" s="2">
+      <c r="P182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q182" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="P182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q182" t="s" s="2">
-        <v>594</v>
-      </c>
       <c r="R182" t="s" s="2">
         <v>78</v>
       </c>
@@ -24450,7 +24446,7 @@
         <v>78</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -24471,21 +24467,21 @@
         <v>78</v>
       </c>
       <c r="AM182" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AN182" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO182" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="AN182" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO182" t="s" s="2">
-        <v>596</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24508,19 +24504,19 @@
         <v>78</v>
       </c>
       <c r="K183" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="L183" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="L183" t="s" s="2">
+      <c r="M183" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="M183" t="s" s="2">
+      <c r="N183" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="N183" t="s" s="2">
+      <c r="O183" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>78</v>
@@ -24569,7 +24565,7 @@
         <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24587,13 +24583,13 @@
         <v>78</v>
       </c>
       <c r="AL183" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AM183" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="AM183" t="s" s="2">
+      <c r="AN183" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>78</v>
@@ -24601,10 +24597,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24716,10 +24712,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24833,13 +24829,13 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C186" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C186" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="D186" t="s" s="2">
         <v>78</v>
@@ -24861,13 +24857,13 @@
         <v>78</v>
       </c>
       <c r="K186" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L186" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="L186" t="s" s="2">
+      <c r="M186" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -24950,10 +24946,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24979,16 +24975,16 @@
         <v>176</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="N187" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -25017,25 +25013,25 @@
       </c>
       <c r="Y187" s="2"/>
       <c r="Z187" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF187" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -25053,13 +25049,13 @@
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AM187" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="AM187" t="s" s="2">
+      <c r="AN187" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>78</v>
@@ -25067,10 +25063,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25096,16 +25092,16 @@
         <v>104</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="N188" t="s" s="2">
+      <c r="O188" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -25154,7 +25150,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -25172,10 +25168,10 @@
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM188" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>78</v>
@@ -25186,14 +25182,14 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
@@ -25215,13 +25211,13 @@
         <v>104</v>
       </c>
       <c r="L189" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M189" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="M189" t="s" s="2">
+      <c r="N189" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -25271,7 +25267,7 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -25289,13 +25285,13 @@
         <v>78</v>
       </c>
       <c r="AL189" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AM189" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="AM189" t="s" s="2">
+      <c r="AN189" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>78</v>
@@ -25303,14 +25299,14 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
@@ -25332,13 +25328,13 @@
         <v>104</v>
       </c>
       <c r="L190" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M190" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="M190" t="s" s="2">
+      <c r="N190" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
@@ -25388,7 +25384,7 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
@@ -25406,13 +25402,13 @@
         <v>78</v>
       </c>
       <c r="AL190" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AM190" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="AM190" t="s" s="2">
+      <c r="AN190" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>78</v>
@@ -25420,10 +25416,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25449,10 +25445,10 @@
         <v>104</v>
       </c>
       <c r="L191" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M191" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -25482,28 +25478,28 @@
         <v>158</v>
       </c>
       <c r="Y191" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="Z191" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="Z191" t="s" s="2">
+      <c r="AA191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF191" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -25521,13 +25517,13 @@
         <v>78</v>
       </c>
       <c r="AL191" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AM191" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="AM191" t="s" s="2">
+      <c r="AN191" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>78</v>
@@ -25535,10 +25531,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25564,10 +25560,10 @@
         <v>104</v>
       </c>
       <c r="L192" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M192" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -25597,28 +25593,28 @@
         <v>158</v>
       </c>
       <c r="Y192" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="Z192" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="Z192" t="s" s="2">
+      <c r="AA192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF192" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
@@ -25636,10 +25632,10 @@
         <v>78</v>
       </c>
       <c r="AL192" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AM192" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>78</v>
@@ -25650,10 +25646,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25679,14 +25675,14 @@
         <v>253</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>78</v>
@@ -25735,7 +25731,7 @@
         <v>78</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -25753,10 +25749,10 @@
         <v>78</v>
       </c>
       <c r="AL193" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AM193" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>534</v>
@@ -25767,10 +25763,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25793,19 +25789,19 @@
         <v>78</v>
       </c>
       <c r="K194" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="L194" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="L194" t="s" s="2">
+      <c r="M194" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="N194" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="N194" t="s" s="2">
+      <c r="O194" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>78</v>
@@ -25842,7 +25838,7 @@
         <v>78</v>
       </c>
       <c r="AB194" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AC194" s="2"/>
       <c r="AD194" t="s" s="2">
@@ -25852,7 +25848,7 @@
         <v>117</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
@@ -25864,19 +25860,19 @@
         <v>209</v>
       </c>
       <c r="AJ194" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AK194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL194" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="AK194" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL194" t="s" s="2">
+      <c r="AM194" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="AM194" t="s" s="2">
+      <c r="AN194" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="AN194" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>78</v>
@@ -25884,10 +25880,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25999,10 +25995,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26116,13 +26112,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C197" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="C197" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>78</v>
@@ -26144,13 +26140,13 @@
         <v>78</v>
       </c>
       <c r="K197" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="L197" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="L197" t="s" s="2">
+      <c r="M197" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -26233,10 +26229,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26262,10 +26258,10 @@
         <v>176</v>
       </c>
       <c r="L198" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M198" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -26295,37 +26291,37 @@
         <v>236</v>
       </c>
       <c r="Y198" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="Z198" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="Z198" t="s" s="2">
+      <c r="AA198" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB198" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC198" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD198" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE198" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF198" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="AA198" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB198" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC198" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD198" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE198" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF198" t="s" s="2">
+      <c r="AG198" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH198" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI198" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="AG198" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH198" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI198" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="AJ198" t="s" s="2">
         <v>102</v>
@@ -26334,13 +26330,13 @@
         <v>78</v>
       </c>
       <c r="AL198" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AM198" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="AM198" t="s" s="2">
+      <c r="AN198" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="AN198" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>78</v>
@@ -26348,10 +26344,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26377,16 +26373,16 @@
         <v>104</v>
       </c>
       <c r="L199" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M199" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M199" t="s" s="2">
+      <c r="N199" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="N199" t="s" s="2">
+      <c r="O199" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="O199" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>78</v>
@@ -26435,7 +26431,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26453,10 +26449,10 @@
         <v>78</v>
       </c>
       <c r="AL199" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AM199" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="AM199" t="s" s="2">
-        <v>708</v>
       </c>
       <c r="AN199" t="s" s="2">
         <v>527</v>
@@ -26467,10 +26463,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26496,16 +26492,16 @@
         <v>176</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="M200" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="M200" t="s" s="2">
+      <c r="N200" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="N200" t="s" s="2">
+      <c r="O200" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>78</v>
@@ -26533,28 +26529,28 @@
         <v>236</v>
       </c>
       <c r="Y200" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="Z200" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="Z200" t="s" s="2">
+      <c r="AA200" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB200" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC200" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD200" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE200" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF200" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="AA200" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB200" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC200" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD200" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE200" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF200" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26572,13 +26568,13 @@
         <v>78</v>
       </c>
       <c r="AL200" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AM200" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AN200" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="AM200" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="AN200" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>78</v>
@@ -26586,10 +26582,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26612,16 +26608,16 @@
         <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="L201" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="L201" t="s" s="2">
+      <c r="M201" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="M201" t="s" s="2">
+      <c r="N201" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -26671,7 +26667,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -26703,10 +26699,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26732,10 +26728,10 @@
         <v>253</v>
       </c>
       <c r="L202" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M202" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M202" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -26786,7 +26782,7 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
@@ -26807,7 +26803,7 @@
         <v>199</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>534</v>
@@ -26818,13 +26814,13 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C203" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="C203" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="D203" t="s" s="2">
         <v>78</v>
@@ -26846,19 +26842,19 @@
         <v>78</v>
       </c>
       <c r="K203" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="L203" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="L203" t="s" s="2">
-        <v>732</v>
-      </c>
       <c r="M203" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="N203" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="N203" t="s" s="2">
+      <c r="O203" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="O203" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>78</v>
@@ -26907,7 +26903,7 @@
         <v>78</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -26919,19 +26915,19 @@
         <v>209</v>
       </c>
       <c r="AJ203" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AK203" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL203" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="AK203" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL203" t="s" s="2">
+      <c r="AM203" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="AM203" t="s" s="2">
+      <c r="AN203" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="AN203" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>78</v>
@@ -26939,10 +26935,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26965,19 +26961,19 @@
         <v>78</v>
       </c>
       <c r="K204" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="L204" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="L204" t="s" s="2">
+      <c r="M204" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="M204" t="s" s="2">
+      <c r="N204" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="N204" t="s" s="2">
+      <c r="O204" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>78</v>
@@ -27026,7 +27022,7 @@
         <v>78</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
@@ -27044,13 +27040,13 @@
         <v>78</v>
       </c>
       <c r="AL204" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="AM204" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="AM204" t="s" s="2">
+      <c r="AN204" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="AN204" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>78</v>
@@ -27058,10 +27054,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27087,14 +27083,14 @@
         <v>176</v>
       </c>
       <c r="L205" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M205" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="M205" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>78</v>
@@ -27122,11 +27118,11 @@
         <v>236</v>
       </c>
       <c r="Y205" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="Z205" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="Z205" t="s" s="2">
-        <v>747</v>
-      </c>
       <c r="AA205" t="s" s="2">
         <v>78</v>
       </c>
@@ -27143,7 +27139,7 @@
         <v>78</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
@@ -27161,13 +27157,13 @@
         <v>78</v>
       </c>
       <c r="AL205" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="AM205" t="s" s="2">
         <v>748</v>
       </c>
-      <c r="AM205" t="s" s="2">
+      <c r="AN205" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="AN205" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>78</v>
@@ -27175,10 +27171,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27201,17 +27197,17 @@
         <v>91</v>
       </c>
       <c r="K206" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="L206" t="s" s="2">
         <v>752</v>
       </c>
-      <c r="L206" t="s" s="2">
+      <c r="M206" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="M206" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>78</v>
@@ -27260,7 +27256,7 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
@@ -27278,13 +27274,13 @@
         <v>78</v>
       </c>
       <c r="AL206" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AM206" t="s" s="2">
         <v>756</v>
       </c>
-      <c r="AM206" t="s" s="2">
+      <c r="AN206" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="AN206" t="s" s="2">
-        <v>758</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>78</v>
@@ -27292,10 +27288,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27321,14 +27317,14 @@
         <v>412</v>
       </c>
       <c r="L207" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="M207" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="M207" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="P207" t="s" s="2">
         <v>78</v>
@@ -27377,7 +27373,7 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
@@ -27398,10 +27394,10 @@
         <v>78</v>
       </c>
       <c r="AM207" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="AN207" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="AN207" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>78</v>
@@ -27409,10 +27405,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27435,13 +27431,13 @@
         <v>78</v>
       </c>
       <c r="K208" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="L208" t="s" s="2">
         <v>766</v>
       </c>
-      <c r="L208" t="s" s="2">
+      <c r="M208" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="M208" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -27480,7 +27476,7 @@
         <v>78</v>
       </c>
       <c r="AB208" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AC208" s="2"/>
       <c r="AD208" t="s" s="2">
@@ -27490,7 +27486,7 @@
         <v>117</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27508,13 +27504,13 @@
         <v>78</v>
       </c>
       <c r="AL208" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AM208" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="AM208" t="s" s="2">
+      <c r="AN208" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="AN208" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>78</v>
@@ -27522,10 +27518,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27637,10 +27633,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27754,14 +27750,14 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
@@ -27783,10 +27779,10 @@
         <v>111</v>
       </c>
       <c r="L211" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="M211" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M211" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="N211" t="s" s="2">
         <v>114</v>
@@ -27841,7 +27837,7 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -27873,10 +27869,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -27902,14 +27898,14 @@
         <v>422</v>
       </c>
       <c r="L212" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M212" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="M212" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
@@ -27958,7 +27954,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -27979,7 +27975,7 @@
         <v>78</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AN212" t="s" s="2">
         <v>78</v>
@@ -27990,10 +27986,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28019,10 +28015,10 @@
         <v>233</v>
       </c>
       <c r="L213" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M213" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="M213" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -28053,7 +28049,7 @@
       </c>
       <c r="Y213" s="2"/>
       <c r="Z213" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>78</v>
@@ -28071,7 +28067,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>90</v>
@@ -28092,10 +28088,10 @@
         <v>78</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>78</v>
@@ -28103,10 +28099,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28132,14 +28128,14 @@
         <v>253</v>
       </c>
       <c r="L214" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="M214" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="M214" t="s" s="2">
-        <v>792</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28188,7 +28184,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28209,10 +28205,10 @@
         <v>78</v>
       </c>
       <c r="AM214" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="AN214" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="AN214" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28220,10 +28216,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28249,10 +28245,10 @@
         <v>536</v>
       </c>
       <c r="L215" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="M215" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="M215" t="s" s="2">
-        <v>798</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -28303,7 +28299,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28324,7 +28320,7 @@
         <v>78</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AN215" t="s" s="2">
         <v>78</v>
@@ -28335,13 +28331,13 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="C216" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="B216" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="C216" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="D216" t="s" s="2">
         <v>78</v>
@@ -28363,13 +28359,13 @@
         <v>78</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -28420,7 +28416,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28438,13 +28434,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AM216" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="AM216" t="s" s="2">
+      <c r="AN216" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="AN216" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28452,10 +28448,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28567,10 +28563,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28680,13 +28676,13 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="C219" t="s" s="2">
         <v>805</v>
-      </c>
-      <c r="B219" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="C219" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="D219" t="s" s="2">
         <v>78</v>
@@ -28708,13 +28704,13 @@
         <v>78</v>
       </c>
       <c r="K219" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="L219" t="s" s="2">
         <v>807</v>
       </c>
-      <c r="L219" t="s" s="2">
+      <c r="M219" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="M219" t="s" s="2">
-        <v>809</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -28797,10 +28793,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="B220" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="B220" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -28912,10 +28908,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="B221" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="B221" t="s" s="2">
-        <v>813</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29029,13 +29025,13 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="C222" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="B222" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="C222" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>78</v>
@@ -29146,10 +29142,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="B223" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="B223" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29261,10 +29257,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="B224" t="s" s="2">
         <v>818</v>
-      </c>
-      <c r="B224" t="s" s="2">
-        <v>819</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29376,10 +29372,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="B225" t="s" s="2">
         <v>820</v>
-      </c>
-      <c r="B225" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29419,7 +29415,7 @@
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="S225" t="s" s="2">
         <v>78</v>
@@ -29493,10 +29489,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="B226" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29556,7 +29552,7 @@
       </c>
       <c r="Y226" s="2"/>
       <c r="Z226" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>78</v>
@@ -29606,13 +29602,13 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="C227" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="C227" t="s" s="2">
-        <v>826</v>
       </c>
       <c r="D227" t="s" s="2">
         <v>78</v>
@@ -29723,10 +29719,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29838,10 +29834,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -29953,10 +29949,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -29996,7 +29992,7 @@
       </c>
       <c r="Q230" s="2"/>
       <c r="R230" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="S230" t="s" s="2">
         <v>78</v>
@@ -30070,10 +30066,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30133,7 +30129,7 @@
       </c>
       <c r="Y231" s="2"/>
       <c r="Z231" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>78</v>
@@ -30183,13 +30179,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="C232" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="C232" t="s" s="2">
-        <v>833</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30300,10 +30296,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30415,10 +30411,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30530,10 +30526,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30573,7 +30569,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>78</v>
@@ -30647,10 +30643,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30710,7 +30706,7 @@
       </c>
       <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>78</v>
@@ -30760,10 +30756,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="B237" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -30803,7 +30799,7 @@
       </c>
       <c r="Q237" s="2"/>
       <c r="R237" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="S237" t="s" s="2">
         <v>78</v>
@@ -30877,10 +30873,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="B238" t="s" s="2">
         <v>842</v>
-      </c>
-      <c r="B238" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -30992,14 +30988,14 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
@@ -31021,10 +31017,10 @@
         <v>111</v>
       </c>
       <c r="L239" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="M239" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M239" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="N239" t="s" s="2">
         <v>114</v>
@@ -31079,7 +31075,7 @@
         <v>78</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>79</v>
@@ -31111,10 +31107,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31140,14 +31136,14 @@
         <v>422</v>
       </c>
       <c r="L240" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M240" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="M240" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>78</v>
@@ -31196,7 +31192,7 @@
         <v>78</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>79</v>
@@ -31217,7 +31213,7 @@
         <v>78</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AN240" t="s" s="2">
         <v>78</v>
@@ -31228,10 +31224,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31257,10 +31253,10 @@
         <v>233</v>
       </c>
       <c r="L241" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M241" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -31291,7 +31287,7 @@
       </c>
       <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>78</v>
@@ -31309,7 +31305,7 @@
         <v>78</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>90</v>
@@ -31330,10 +31326,10 @@
         <v>78</v>
       </c>
       <c r="AM241" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AN241" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AO241" t="s" s="2">
         <v>78</v>
@@ -31341,10 +31337,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="B242" t="s" s="2">
         <v>847</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>848</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -31456,10 +31452,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="B243" t="s" s="2">
         <v>849</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>850</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31573,10 +31569,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="B244" t="s" s="2">
         <v>851</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>852</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31648,14 +31644,14 @@
         <v>78</v>
       </c>
       <c r="AB244" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AC244" s="2"/>
       <c r="AD244" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE244" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AF244" t="s" s="2">
         <v>458</v>
@@ -31690,13 +31686,13 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
+        <v>854</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="C245" t="s" s="2">
         <v>855</v>
-      </c>
-      <c r="B245" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="C245" t="s" s="2">
-        <v>856</v>
       </c>
       <c r="D245" t="s" s="2">
         <v>78</v>
@@ -31759,7 +31755,7 @@
       </c>
       <c r="Y245" s="2"/>
       <c r="Z245" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>78</v>
@@ -31809,13 +31805,13 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D246" t="s" s="2">
         <v>78</v>
@@ -31878,7 +31874,7 @@
       </c>
       <c r="Y246" s="2"/>
       <c r="Z246" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>78</v>
@@ -31928,10 +31924,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="B247" t="s" s="2">
         <v>859</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>860</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32047,10 +32043,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32076,14 +32072,14 @@
         <v>253</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>78</v>
@@ -32132,7 +32128,7 @@
         <v>78</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>79</v>
@@ -32153,10 +32149,10 @@
         <v>78</v>
       </c>
       <c r="AM248" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="AN248" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="AN248" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="AO248" t="s" s="2">
         <v>78</v>
@@ -32164,10 +32160,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="B249" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32279,10 +32275,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="B250" t="s" s="2">
         <v>865</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>866</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32396,10 +32392,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="B251" t="s" s="2">
         <v>867</v>
-      </c>
-      <c r="B251" t="s" s="2">
-        <v>868</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32425,7 +32421,7 @@
         <v>260</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="M251" t="s" s="2">
         <v>262</v>
@@ -32513,10 +32509,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="B252" t="s" s="2">
         <v>870</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>871</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32542,7 +32538,7 @@
         <v>260</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="M252" t="s" s="2">
         <v>271</v>
@@ -32632,10 +32628,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32658,13 +32654,13 @@
         <v>78</v>
       </c>
       <c r="K253" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="L253" t="s" s="2">
         <v>874</v>
       </c>
-      <c r="L253" t="s" s="2">
-        <v>875</v>
-      </c>
       <c r="M253" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
@@ -32715,7 +32711,7 @@
         <v>78</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>79</v>
@@ -32736,7 +32732,7 @@
         <v>78</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>78</v>
@@ -32747,13 +32743,13 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="C254" t="s" s="2">
         <v>876</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="C254" t="s" s="2">
-        <v>877</v>
       </c>
       <c r="D254" t="s" s="2">
         <v>78</v>
@@ -32775,13 +32771,13 @@
         <v>78</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
@@ -32832,7 +32828,7 @@
         <v>78</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>79</v>
@@ -32850,13 +32846,13 @@
         <v>78</v>
       </c>
       <c r="AL254" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AM254" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="AM254" t="s" s="2">
+      <c r="AN254" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="AN254" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="AO254" t="s" s="2">
         <v>78</v>
@@ -32864,10 +32860,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -32979,10 +32975,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -33096,14 +33092,14 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
@@ -33125,10 +33121,10 @@
         <v>111</v>
       </c>
       <c r="L257" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="M257" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M257" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="N257" t="s" s="2">
         <v>114</v>
@@ -33183,7 +33179,7 @@
         <v>78</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>79</v>
@@ -33215,10 +33211,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33244,14 +33240,14 @@
         <v>422</v>
       </c>
       <c r="L258" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M258" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="M258" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>78</v>
@@ -33300,7 +33296,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33321,7 +33317,7 @@
         <v>78</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AN258" t="s" s="2">
         <v>78</v>
@@ -33332,10 +33328,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33361,10 +33357,10 @@
         <v>233</v>
       </c>
       <c r="L259" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M259" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="M259" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="N259" s="2"/>
       <c r="O259" s="2"/>
@@ -33395,7 +33391,7 @@
       </c>
       <c r="Y259" s="2"/>
       <c r="Z259" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AA259" t="s" s="2">
         <v>78</v>
@@ -33413,7 +33409,7 @@
         <v>78</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>90</v>
@@ -33434,10 +33430,10 @@
         <v>78</v>
       </c>
       <c r="AM259" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AN259" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AO259" t="s" s="2">
         <v>78</v>
@@ -33445,10 +33441,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33560,10 +33556,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33677,10 +33673,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33752,14 +33748,14 @@
         <v>78</v>
       </c>
       <c r="AB262" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AC262" s="2"/>
       <c r="AD262" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE262" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AF262" t="s" s="2">
         <v>458</v>
@@ -33794,13 +33790,13 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="C263" t="s" s="2">
         <v>887</v>
-      </c>
-      <c r="B263" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="C263" t="s" s="2">
-        <v>888</v>
       </c>
       <c r="D263" t="s" s="2">
         <v>78</v>
@@ -33825,7 +33821,7 @@
         <v>154</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="M263" t="s" s="2">
         <v>455</v>
@@ -33863,7 +33859,7 @@
       </c>
       <c r="Y263" s="2"/>
       <c r="Z263" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="AA263" t="s" s="2">
         <v>78</v>
@@ -33913,10 +33909,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C264" t="s" s="2">
         <v>337</v>
@@ -33944,7 +33940,7 @@
         <v>154</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="M264" t="s" s="2">
         <v>455</v>
@@ -34032,10 +34028,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34151,10 +34147,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34180,14 +34176,14 @@
         <v>253</v>
       </c>
       <c r="L266" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="M266" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="M266" t="s" s="2">
-        <v>792</v>
       </c>
       <c r="N266" s="2"/>
       <c r="O266" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>78</v>
@@ -34236,7 +34232,7 @@
         <v>78</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>79</v>
@@ -34257,10 +34253,10 @@
         <v>78</v>
       </c>
       <c r="AM266" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="AN266" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="AN266" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="AO266" t="s" s="2">
         <v>78</v>
@@ -34268,10 +34264,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -34383,10 +34379,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34500,10 +34496,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34529,7 +34525,7 @@
         <v>260</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="M269" t="s" s="2">
         <v>262</v>
@@ -34617,10 +34613,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34646,7 +34642,7 @@
         <v>260</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M270" t="s" s="2">
         <v>271</v>
@@ -34736,10 +34732,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34765,10 +34761,10 @@
         <v>536</v>
       </c>
       <c r="L271" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="M271" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="M271" t="s" s="2">
-        <v>798</v>
       </c>
       <c r="N271" s="2"/>
       <c r="O271" s="2"/>
@@ -34819,7 +34815,7 @@
         <v>78</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>79</v>
@@ -34840,7 +34836,7 @@
         <v>78</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AN271" t="s" s="2">
         <v>78</v>
@@ -34851,13 +34847,13 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="C272" t="s" s="2">
         <v>902</v>
-      </c>
-      <c r="B272" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="C272" t="s" s="2">
-        <v>903</v>
       </c>
       <c r="D272" t="s" s="2">
         <v>78</v>
@@ -34879,13 +34875,13 @@
         <v>78</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="N272" s="2"/>
       <c r="O272" s="2"/>
@@ -34936,7 +34932,7 @@
         <v>78</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>79</v>
@@ -34954,13 +34950,13 @@
         <v>78</v>
       </c>
       <c r="AL272" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AM272" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="AM272" t="s" s="2">
+      <c r="AN272" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="AN272" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="AO272" t="s" s="2">
         <v>78</v>
@@ -34968,10 +34964,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -35083,10 +35079,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -35200,14 +35196,14 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E275" s="2"/>
       <c r="F275" t="s" s="2">
@@ -35229,10 +35225,10 @@
         <v>111</v>
       </c>
       <c r="L275" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="M275" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M275" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="N275" t="s" s="2">
         <v>114</v>
@@ -35287,7 +35283,7 @@
         <v>78</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>79</v>
@@ -35319,10 +35315,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35348,14 +35344,14 @@
         <v>422</v>
       </c>
       <c r="L276" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M276" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="M276" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>78</v>
@@ -35404,7 +35400,7 @@
         <v>78</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>79</v>
@@ -35425,7 +35421,7 @@
         <v>78</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AN276" t="s" s="2">
         <v>78</v>
@@ -35436,10 +35432,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35465,10 +35461,10 @@
         <v>233</v>
       </c>
       <c r="L277" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M277" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="M277" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="N277" s="2"/>
       <c r="O277" s="2"/>
@@ -35499,7 +35495,7 @@
       </c>
       <c r="Y277" s="2"/>
       <c r="Z277" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AA277" t="s" s="2">
         <v>78</v>
@@ -35517,7 +35513,7 @@
         <v>78</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>90</v>
@@ -35532,16 +35528,16 @@
         <v>102</v>
       </c>
       <c r="AK277" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="AL277" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM277" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AN277" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AO277" t="s" s="2">
         <v>78</v>
@@ -35549,10 +35545,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35664,10 +35660,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35781,10 +35777,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35856,7 +35852,7 @@
         <v>78</v>
       </c>
       <c r="AB280" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AC280" s="2"/>
       <c r="AD280" t="s" s="2">
@@ -35898,13 +35894,13 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D281" t="s" s="2">
         <v>78</v>
@@ -35929,7 +35925,7 @@
         <v>154</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="M281" t="s" s="2">
         <v>455</v>
@@ -35967,7 +35963,7 @@
       </c>
       <c r="Y281" s="2"/>
       <c r="Z281" t="s" s="2">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="AA281" t="s" s="2">
         <v>78</v>
@@ -36017,13 +36013,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36048,7 +36044,7 @@
         <v>154</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="M282" t="s" s="2">
         <v>455</v>
@@ -36086,7 +36082,7 @@
       </c>
       <c r="Y282" s="2"/>
       <c r="Z282" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="AA282" t="s" s="2">
         <v>78</v>
@@ -36136,10 +36132,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36255,10 +36251,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36284,14 +36280,14 @@
         <v>253</v>
       </c>
       <c r="L284" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="M284" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="M284" t="s" s="2">
-        <v>792</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P284" t="s" s="2">
         <v>78</v>
@@ -36340,7 +36336,7 @@
         <v>78</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AG284" t="s" s="2">
         <v>79</v>
@@ -36361,10 +36357,10 @@
         <v>78</v>
       </c>
       <c r="AM284" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="AN284" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="AN284" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="AO284" t="s" s="2">
         <v>78</v>
@@ -36372,10 +36368,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -36487,10 +36483,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36604,10 +36600,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36633,7 +36629,7 @@
         <v>260</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="M287" t="s" s="2">
         <v>262</v>
@@ -36704,7 +36700,7 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>266</v>
@@ -36721,10 +36717,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36750,7 +36746,7 @@
         <v>260</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M288" t="s" s="2">
         <v>271</v>
@@ -36823,7 +36819,7 @@
         <v>102</v>
       </c>
       <c r="AK288" t="s" s="2">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AL288" t="s" s="2">
         <v>275</v>
@@ -36840,10 +36836,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -36869,10 +36865,10 @@
         <v>536</v>
       </c>
       <c r="L289" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="M289" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="M289" t="s" s="2">
-        <v>798</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="2"/>
@@ -36923,7 +36919,7 @@
         <v>78</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>79</v>
@@ -36944,7 +36940,7 @@
         <v>78</v>
       </c>
       <c r="AM289" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AN289" t="s" s="2">
         <v>78</v>
@@ -36955,10 +36951,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -36981,19 +36977,19 @@
         <v>78</v>
       </c>
       <c r="K290" t="s" s="2">
+        <v>931</v>
+      </c>
+      <c r="L290" t="s" s="2">
         <v>932</v>
       </c>
-      <c r="L290" t="s" s="2">
+      <c r="M290" t="s" s="2">
         <v>933</v>
       </c>
-      <c r="M290" t="s" s="2">
+      <c r="N290" t="s" s="2">
         <v>934</v>
       </c>
-      <c r="N290" t="s" s="2">
+      <c r="O290" t="s" s="2">
         <v>935</v>
-      </c>
-      <c r="O290" t="s" s="2">
-        <v>936</v>
       </c>
       <c r="P290" t="s" s="2">
         <v>78</v>
@@ -37022,7 +37018,7 @@
       </c>
       <c r="Y290" s="2"/>
       <c r="Z290" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="AA290" t="s" s="2">
         <v>78</v>
@@ -37040,7 +37036,7 @@
         <v>78</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>79</v>
@@ -37058,10 +37054,10 @@
         <v>78</v>
       </c>
       <c r="AL290" t="s" s="2">
+        <v>937</v>
+      </c>
+      <c r="AM290" t="s" s="2">
         <v>938</v>
-      </c>
-      <c r="AM290" t="s" s="2">
-        <v>939</v>
       </c>
       <c r="AN290" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10691" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10691" uniqueCount="940">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -686,7 +686,7 @@
     <t>InscriptionOrdre : Eléments permettant de retrouver les informations d'inscription à un ordre par rapport à la profession de la personne physique sur une période et un département donné.</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true".</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true". Ces données sont uniquement accessibles en accès restreint.</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-registration.id</t>
@@ -2407,7 +2407,7 @@
     <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:code}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -2663,111 +2663,111 @@
     <t>Practitioner.qualification.code.coding</t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degreeType</t>
+  </si>
+  <si>
+    <t>degreeType</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degree</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period</t>
+  </si>
+  <si>
+    <t>[Donnée restreinte] : Période durant laquelle le niveau de formation est actif.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.start</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.start</t>
+  </si>
+  <si>
+    <t>dateDebut : Date d’obtention du diplôme (dateDiplome)
+cette date est renseignée par l’ordre à la clôture de l’exercice professionnel.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.end</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.end</t>
+  </si>
+  <si>
+    <t>dateFin : Date à laquelle le niveau de formation n’est plus actif (non visible hormis dans les données historisées).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.issuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+</t>
+  </si>
+  <si>
+    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.coding:degreeType</t>
-  </si>
-  <si>
-    <t>degreeType</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.coding:degree</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Période durant laquelle le niveau de formation est actif.</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.start</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.start</t>
-  </si>
-  <si>
-    <t>dateDebut : Date d’obtention du diplôme (dateDiplome)
-cette date est renseignée par l’ordre à la clôture de l’exercice professionnel.</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.end</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.end</t>
-  </si>
-  <si>
-    <t>dateFin : Date à laquelle le niveau de formation n’est plus actif (non visible hormis dans les données historisées).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.issuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
-</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro</t>
-  </si>
-  <si>
-    <t>exercicePro</t>
-  </si>
-  <si>
-    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.coding</t>
-  </si>
-  <si>
     <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
   </si>
   <si>
@@ -2819,7 +2819,7 @@
     <t>savoirFaire</t>
   </si>
   <si>
-    <t>savoirFAire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
+    <t>savoirFaire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.id</t>
@@ -2837,19 +2837,22 @@
     <t>Practitioner.qualification:savoirFaire.code</t>
   </si>
   <si>
+    <t>SavoirFaire.typeSavoirFaire</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding:typeSavoirFaire</t>
+  </si>
+  <si>
     <t>typeSavoirFaire</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>Le type de savoir-faire (qualifications/autres attributions).
@@ -2886,7 +2889,7 @@
     <t>Starting time with inclusive boundary</t>
   </si>
   <si>
-    <t>dateReconnaissance</t>
+    <t>SavoirFaire.dateReconnaissance</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.period.end</t>
@@ -2895,7 +2898,7 @@
     <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
-    <t>dateAbandon</t>
+    <t>SavoirFaire.dateAbandon</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.issuer</t>
@@ -31644,14 +31647,14 @@
         <v>78</v>
       </c>
       <c r="AB244" t="s" s="2">
-        <v>852</v>
+        <v>768</v>
       </c>
       <c r="AC244" s="2"/>
       <c r="AD244" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE244" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AF244" t="s" s="2">
         <v>458</v>
@@ -31686,13 +31689,13 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>851</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D245" t="s" s="2">
         <v>78</v>
@@ -31755,7 +31758,7 @@
       </c>
       <c r="Y245" s="2"/>
       <c r="Z245" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>78</v>
@@ -31805,7 +31808,7 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>851</v>
@@ -31924,10 +31927,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="B247" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>859</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32043,7 +32046,7 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>789</v>
@@ -32072,7 +32075,7 @@
         <v>253</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="M248" t="s" s="2">
         <v>791</v>
@@ -32160,10 +32163,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="B249" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32275,10 +32278,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="B250" t="s" s="2">
         <v>864</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>865</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32392,10 +32395,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="B251" t="s" s="2">
         <v>866</v>
-      </c>
-      <c r="B251" t="s" s="2">
-        <v>867</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32421,7 +32424,7 @@
         <v>260</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="M251" t="s" s="2">
         <v>262</v>
@@ -32509,10 +32512,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="B252" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32538,7 +32541,7 @@
         <v>260</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="M252" t="s" s="2">
         <v>271</v>
@@ -32628,7 +32631,7 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>795</v>
@@ -32654,10 +32657,10 @@
         <v>78</v>
       </c>
       <c r="K253" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="L253" t="s" s="2">
         <v>873</v>
-      </c>
-      <c r="L253" t="s" s="2">
-        <v>874</v>
       </c>
       <c r="M253" t="s" s="2">
         <v>797</v>
@@ -32743,13 +32746,13 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>764</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D254" t="s" s="2">
         <v>78</v>
@@ -32774,7 +32777,7 @@
         <v>765</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="M254" t="s" s="2">
         <v>767</v>
@@ -32860,7 +32863,7 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>772</v>
@@ -32975,7 +32978,7 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>773</v>
@@ -33092,7 +33095,7 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>774</v>
@@ -33211,7 +33214,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>779</v>
@@ -33328,7 +33331,7 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>784</v>
@@ -33441,7 +33444,7 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>847</v>
@@ -33556,7 +33559,7 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>849</v>
@@ -33673,7 +33676,7 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>851</v>
@@ -33748,14 +33751,14 @@
         <v>78</v>
       </c>
       <c r="AB262" t="s" s="2">
-        <v>852</v>
+        <v>885</v>
       </c>
       <c r="AC262" s="2"/>
       <c r="AD262" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE262" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AF262" t="s" s="2">
         <v>458</v>
@@ -34031,7 +34034,7 @@
         <v>892</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34267,7 +34270,7 @@
         <v>894</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -34382,7 +34385,7 @@
         <v>895</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34499,7 +34502,7 @@
         <v>896</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34616,7 +34619,7 @@
         <v>898</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -35852,7 +35855,7 @@
         <v>78</v>
       </c>
       <c r="AB280" t="s" s="2">
-        <v>852</v>
+        <v>885</v>
       </c>
       <c r="AC280" s="2"/>
       <c r="AD280" t="s" s="2">
@@ -35900,7 +35903,7 @@
         <v>851</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="D281" t="s" s="2">
         <v>78</v>
@@ -35925,7 +35928,7 @@
         <v>154</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="M281" t="s" s="2">
         <v>455</v>
@@ -35963,7 +35966,7 @@
       </c>
       <c r="Y281" s="2"/>
       <c r="Z281" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="AA281" t="s" s="2">
         <v>78</v>
@@ -36013,7 +36016,7 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>851</v>
@@ -36044,7 +36047,7 @@
         <v>154</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="M282" t="s" s="2">
         <v>455</v>
@@ -36082,7 +36085,7 @@
       </c>
       <c r="Y282" s="2"/>
       <c r="Z282" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="AA282" t="s" s="2">
         <v>78</v>
@@ -36132,10 +36135,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36251,7 +36254,7 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>789</v>
@@ -36368,10 +36371,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -36483,10 +36486,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36600,10 +36603,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36629,7 +36632,7 @@
         <v>260</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="M287" t="s" s="2">
         <v>262</v>
@@ -36700,7 +36703,7 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>266</v>
@@ -36717,10 +36720,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36746,7 +36749,7 @@
         <v>260</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M288" t="s" s="2">
         <v>271</v>
@@ -36819,7 +36822,7 @@
         <v>102</v>
       </c>
       <c r="AK288" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AL288" t="s" s="2">
         <v>275</v>
@@ -36836,7 +36839,7 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>795</v>
@@ -36951,10 +36954,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -36977,19 +36980,19 @@
         <v>78</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N290" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="O290" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="P290" t="s" s="2">
         <v>78</v>
@@ -37018,7 +37021,7 @@
       </c>
       <c r="Y290" s="2"/>
       <c r="Z290" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AA290" t="s" s="2">
         <v>78</v>
@@ -37036,7 +37039,7 @@
         <v>78</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>79</v>
@@ -37054,10 +37057,10 @@
         <v>78</v>
       </c>
       <c r="AL290" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="AM290" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AN290" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -28553,7 +28553,7 @@
         <v>85</v>
       </c>
       <c r="G188" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H188" t="s" s="2">
         <v>84</v>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -26652,7 +26652,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G174" t="s" s="2">
         <v>102</v>
@@ -27337,7 +27337,7 @@
         <v>102</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>84</v>
@@ -27871,7 +27871,7 @@
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G183" t="s" s="2">
         <v>102</v>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AU$349</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AU$354</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14927" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15138" uniqueCount="1063">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2847,6 +2847,30 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J88-AnneeUniversitaire-RASS/FHIR/JDV-J88-AnneeUniversitaire-RASS|20251016120000</t>
   </si>
   <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation</t>
+  </si>
+  <si>
+    <t>trainingLocation</t>
+  </si>
+  <si>
+    <t>Diplome.lieuFormation</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.url</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension:as-ext-education-level.extension:trainingLocation.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J235-LieuFormation-EPARS/FHIR/JDV-J235-LieuFormation-EPARS|20240726120000</t>
+  </si>
+  <si>
     <t>Practitioner.qualification:degree.extension:as-ext-education-level.url</t>
   </si>
   <si>
@@ -2999,16 +3023,6 @@
   </si>
   <si>
     <t>Practitioner.qualification:degree.issuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
-</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
-  </si>
-  <si>
-    <t>Diplome.lieuFormation</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro</t>
@@ -3603,7 +3617,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AU349"/>
+  <dimension ref="A1:AU354"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="82.7265625" customWidth="true" bestFit="true"/>
@@ -41089,26 +41103,28 @@
         <v>84</v>
       </c>
     </row>
-    <row r="280" hidden="true">
+    <row r="280">
       <c r="A280" t="s" s="2">
         <v>912</v>
       </c>
       <c r="B280" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="C280" t="s" s="2">
         <v>913</v>
       </c>
-      <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E280" s="2"/>
       <c r="F280" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G280" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H280" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I280" t="s" s="2">
         <v>84</v>
@@ -41117,91 +41133,89 @@
         <v>84</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N280" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N280" s="2"/>
       <c r="O280" s="2"/>
       <c r="P280" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q280" s="2"/>
       <c r="R280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF280" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG280" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH280" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ280" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM280" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN280" t="s" s="2">
         <v>914</v>
       </c>
-      <c r="S280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF280" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AG280" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AH280" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM280" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN280" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AO280" t="s" s="2">
         <v>84</v>
       </c>
@@ -41215,7 +41229,7 @@
         <v>84</v>
       </c>
       <c r="AS280" t="s" s="2">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="AT280" t="s" s="2">
         <v>84</v>
@@ -41229,7 +41243,7 @@
         <v>915</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>916</v>
+        <v>888</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -41240,7 +41254,7 @@
         <v>85</v>
       </c>
       <c r="G281" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H281" t="s" s="2">
         <v>84</v>
@@ -41252,13 +41266,13 @@
         <v>84</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>325</v>
+        <v>116</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>252</v>
+        <v>117</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
@@ -41309,7 +41323,7 @@
         <v>84</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>256</v>
+        <v>119</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>85</v>
@@ -41321,7 +41335,7 @@
         <v>84</v>
       </c>
       <c r="AJ281" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK281" t="s" s="2">
         <v>84</v>
@@ -41348,7 +41362,7 @@
         <v>84</v>
       </c>
       <c r="AS281" t="s" s="2">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="AT281" t="s" s="2">
         <v>84</v>
@@ -41359,46 +41373,42 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>842</v>
+        <v>890</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
-        <v>843</v>
+        <v>84</v>
       </c>
       <c r="E282" s="2"/>
       <c r="F282" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G282" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H282" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I282" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="J282" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K282" t="s" s="2">
         <v>123</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>844</v>
+        <v>218</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="N282" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O282" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N282" s="2"/>
+      <c r="O282" s="2"/>
       <c r="P282" t="s" s="2">
         <v>84</v>
       </c>
@@ -41434,19 +41444,19 @@
         <v>84</v>
       </c>
       <c r="AB282" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC282" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD282" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE282" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>846</v>
+        <v>130</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>85</v>
@@ -41485,7 +41495,7 @@
         <v>84</v>
       </c>
       <c r="AS282" t="s" s="2">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="AT282" t="s" s="2">
         <v>84</v>
@@ -41496,10 +41506,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>847</v>
+        <v>892</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -41507,10 +41517,10 @@
       </c>
       <c r="E283" s="2"/>
       <c r="F283" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G283" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H283" t="s" s="2">
         <v>84</v>
@@ -41522,24 +41532,24 @@
         <v>84</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>488</v>
+        <v>149</v>
       </c>
       <c r="L283" t="s" s="2">
-        <v>848</v>
+        <v>245</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="N283" s="2"/>
-      <c r="O283" t="s" s="2">
-        <v>850</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N283" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O283" s="2"/>
       <c r="P283" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q283" s="2"/>
       <c r="R283" t="s" s="2">
-        <v>84</v>
+        <v>913</v>
       </c>
       <c r="S283" t="s" s="2">
         <v>84</v>
@@ -41581,19 +41591,19 @@
         <v>84</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>847</v>
+        <v>248</v>
       </c>
       <c r="AG283" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH283" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI283" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ283" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK283" t="s" s="2">
         <v>84</v>
@@ -41620,7 +41630,7 @@
         <v>84</v>
       </c>
       <c r="AS283" t="s" s="2">
-        <v>851</v>
+        <v>216</v>
       </c>
       <c r="AT283" t="s" s="2">
         <v>84</v>
@@ -41631,10 +41641,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>852</v>
+        <v>894</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -41642,7 +41652,7 @@
       </c>
       <c r="E284" s="2"/>
       <c r="F284" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G284" t="s" s="2">
         <v>102</v>
@@ -41660,10 +41670,10 @@
         <v>251</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>853</v>
+        <v>252</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>854</v>
+        <v>253</v>
       </c>
       <c r="N284" s="2"/>
       <c r="O284" s="2"/>
@@ -41690,13 +41700,11 @@
         <v>84</v>
       </c>
       <c r="X284" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y284" t="s" s="2">
-        <v>855</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y284" s="2"/>
       <c r="Z284" t="s" s="2">
-        <v>856</v>
+        <v>919</v>
       </c>
       <c r="AA284" t="s" s="2">
         <v>84</v>
@@ -41714,10 +41722,10 @@
         <v>84</v>
       </c>
       <c r="AF284" t="s" s="2">
-        <v>852</v>
+        <v>256</v>
       </c>
       <c r="AG284" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AH284" t="s" s="2">
         <v>102</v>
@@ -41753,10 +41761,10 @@
         <v>84</v>
       </c>
       <c r="AS284" t="s" s="2">
-        <v>838</v>
+        <v>216</v>
       </c>
       <c r="AT284" t="s" s="2">
-        <v>858</v>
+        <v>84</v>
       </c>
       <c r="AU284" t="s" s="2">
         <v>84</v>
@@ -41775,7 +41783,7 @@
       </c>
       <c r="E285" s="2"/>
       <c r="F285" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G285" t="s" s="2">
         <v>102</v>
@@ -41790,22 +41798,24 @@
         <v>84</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>117</v>
+        <v>245</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N285" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N285" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="O285" s="2"/>
       <c r="P285" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q285" s="2"/>
       <c r="R285" t="s" s="2">
-        <v>84</v>
+        <v>922</v>
       </c>
       <c r="S285" t="s" s="2">
         <v>84</v>
@@ -41847,10 +41857,10 @@
         <v>84</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>119</v>
+        <v>248</v>
       </c>
       <c r="AG285" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH285" t="s" s="2">
         <v>102</v>
@@ -41886,7 +41896,7 @@
         <v>84</v>
       </c>
       <c r="AS285" t="s" s="2">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="AT285" t="s" s="2">
         <v>84</v>
@@ -41897,21 +41907,21 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E286" s="2"/>
       <c r="F286" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G286" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H286" t="s" s="2">
         <v>84</v>
@@ -41923,17 +41933,15 @@
         <v>84</v>
       </c>
       <c r="K286" t="s" s="2">
-        <v>123</v>
+        <v>325</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>124</v>
+        <v>252</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N286" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N286" s="2"/>
       <c r="O286" s="2"/>
       <c r="P286" t="s" s="2">
         <v>84</v>
@@ -41970,31 +41978,31 @@
         <v>84</v>
       </c>
       <c r="AB286" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC286" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD286" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE286" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>130</v>
+        <v>256</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH286" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI286" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ286" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK286" t="s" s="2">
         <v>84</v>
@@ -42021,7 +42029,7 @@
         <v>84</v>
       </c>
       <c r="AS286" t="s" s="2">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="AT286" t="s" s="2">
         <v>84</v>
@@ -42032,14 +42040,14 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>925</v>
+        <v>842</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
-        <v>84</v>
+        <v>843</v>
       </c>
       <c r="E287" s="2"/>
       <c r="F287" t="s" s="2">
@@ -42052,25 +42060,25 @@
         <v>84</v>
       </c>
       <c r="I287" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J287" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K287" t="s" s="2">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>926</v>
+        <v>844</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>927</v>
+        <v>845</v>
       </c>
       <c r="N287" t="s" s="2">
-        <v>928</v>
+        <v>126</v>
       </c>
       <c r="O287" t="s" s="2">
-        <v>929</v>
+        <v>485</v>
       </c>
       <c r="P287" t="s" s="2">
         <v>84</v>
@@ -42107,17 +42115,19 @@
         <v>84</v>
       </c>
       <c r="AB287" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AC287" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC287" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD287" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE287" t="s" s="2">
-        <v>930</v>
+        <v>84</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>931</v>
+        <v>846</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>85</v>
@@ -42129,7 +42139,7 @@
         <v>84</v>
       </c>
       <c r="AJ287" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK287" t="s" s="2">
         <v>84</v>
@@ -42153,10 +42163,10 @@
         <v>84</v>
       </c>
       <c r="AR287" t="s" s="2">
-        <v>932</v>
+        <v>84</v>
       </c>
       <c r="AS287" t="s" s="2">
-        <v>933</v>
+        <v>216</v>
       </c>
       <c r="AT287" t="s" s="2">
         <v>84</v>
@@ -42165,16 +42175,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="C288" t="s" s="2">
-        <v>935</v>
-      </c>
+        <v>847</v>
+      </c>
+      <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
         <v>84</v>
       </c>
@@ -42183,31 +42191,29 @@
         <v>85</v>
       </c>
       <c r="G288" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H288" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I288" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J288" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K288" t="s" s="2">
-        <v>171</v>
+        <v>488</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>926</v>
+        <v>848</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="N288" t="s" s="2">
-        <v>928</v>
-      </c>
+        <v>849</v>
+      </c>
+      <c r="N288" s="2"/>
       <c r="O288" t="s" s="2">
-        <v>929</v>
+        <v>850</v>
       </c>
       <c r="P288" t="s" s="2">
         <v>84</v>
@@ -42232,11 +42238,13 @@
         <v>84</v>
       </c>
       <c r="X288" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y288" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y288" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z288" t="s" s="2">
-        <v>936</v>
+        <v>84</v>
       </c>
       <c r="AA288" t="s" s="2">
         <v>84</v>
@@ -42254,7 +42262,7 @@
         <v>84</v>
       </c>
       <c r="AF288" t="s" s="2">
-        <v>931</v>
+        <v>847</v>
       </c>
       <c r="AG288" t="s" s="2">
         <v>85</v>
@@ -42290,10 +42298,10 @@
         <v>84</v>
       </c>
       <c r="AR288" t="s" s="2">
-        <v>932</v>
+        <v>84</v>
       </c>
       <c r="AS288" t="s" s="2">
-        <v>933</v>
+        <v>851</v>
       </c>
       <c r="AT288" t="s" s="2">
         <v>84</v>
@@ -42302,50 +42310,44 @@
         <v>84</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>937</v>
+        <v>927</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="C289" t="s" s="2">
-        <v>870</v>
-      </c>
+        <v>852</v>
+      </c>
+      <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E289" s="2"/>
       <c r="F289" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G289" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H289" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I289" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J289" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K289" t="s" s="2">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>926</v>
+        <v>853</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="N289" t="s" s="2">
-        <v>928</v>
-      </c>
-      <c r="O289" t="s" s="2">
-        <v>929</v>
-      </c>
+        <v>854</v>
+      </c>
+      <c r="N289" s="2"/>
+      <c r="O289" s="2"/>
       <c r="P289" t="s" s="2">
         <v>84</v>
       </c>
@@ -42369,11 +42371,13 @@
         <v>84</v>
       </c>
       <c r="X289" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y289" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="Y289" t="s" s="2">
+        <v>855</v>
+      </c>
       <c r="Z289" t="s" s="2">
-        <v>938</v>
+        <v>856</v>
       </c>
       <c r="AA289" t="s" s="2">
         <v>84</v>
@@ -42391,13 +42395,13 @@
         <v>84</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>931</v>
+        <v>852</v>
       </c>
       <c r="AG289" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH289" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI289" t="s" s="2">
         <v>84</v>
@@ -42427,13 +42431,13 @@
         <v>84</v>
       </c>
       <c r="AR289" t="s" s="2">
-        <v>932</v>
+        <v>84</v>
       </c>
       <c r="AS289" t="s" s="2">
-        <v>933</v>
+        <v>838</v>
       </c>
       <c r="AT289" t="s" s="2">
-        <v>84</v>
+        <v>858</v>
       </c>
       <c r="AU289" t="s" s="2">
         <v>84</v>
@@ -42441,10 +42445,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -42464,23 +42468,19 @@
         <v>84</v>
       </c>
       <c r="J290" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K290" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>941</v>
+        <v>117</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>942</v>
-      </c>
-      <c r="N290" t="s" s="2">
-        <v>943</v>
-      </c>
-      <c r="O290" t="s" s="2">
-        <v>944</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N290" s="2"/>
+      <c r="O290" s="2"/>
       <c r="P290" t="s" s="2">
         <v>84</v>
       </c>
@@ -42528,7 +42528,7 @@
         <v>84</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>945</v>
+        <v>119</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>85</v>
@@ -42540,7 +42540,7 @@
         <v>84</v>
       </c>
       <c r="AJ290" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK290" t="s" s="2">
         <v>84</v>
@@ -42564,10 +42564,10 @@
         <v>84</v>
       </c>
       <c r="AR290" t="s" s="2">
-        <v>946</v>
+        <v>84</v>
       </c>
       <c r="AS290" t="s" s="2">
-        <v>947</v>
+        <v>120</v>
       </c>
       <c r="AT290" t="s" s="2">
         <v>84</v>
@@ -42578,21 +42578,21 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>948</v>
+        <v>930</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>859</v>
+        <v>931</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E291" s="2"/>
       <c r="F291" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G291" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H291" t="s" s="2">
         <v>84</v>
@@ -42604,18 +42604,18 @@
         <v>84</v>
       </c>
       <c r="K291" t="s" s="2">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>949</v>
+        <v>124</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="N291" s="2"/>
-      <c r="O291" t="s" s="2">
-        <v>862</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N291" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O291" s="2"/>
       <c r="P291" t="s" s="2">
         <v>84</v>
       </c>
@@ -42651,31 +42651,31 @@
         <v>84</v>
       </c>
       <c r="AB291" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC291" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD291" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE291" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF291" t="s" s="2">
-        <v>859</v>
+        <v>130</v>
       </c>
       <c r="AG291" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH291" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI291" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ291" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK291" t="s" s="2">
         <v>84</v>
@@ -42702,10 +42702,10 @@
         <v>84</v>
       </c>
       <c r="AS291" t="s" s="2">
-        <v>863</v>
+        <v>120</v>
       </c>
       <c r="AT291" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AU291" t="s" s="2">
         <v>84</v>
@@ -42713,10 +42713,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>950</v>
+        <v>932</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>951</v>
+        <v>933</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -42727,7 +42727,7 @@
         <v>85</v>
       </c>
       <c r="G292" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H292" t="s" s="2">
         <v>84</v>
@@ -42736,19 +42736,23 @@
         <v>84</v>
       </c>
       <c r="J292" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K292" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>117</v>
+        <v>934</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N292" s="2"/>
-      <c r="O292" s="2"/>
+        <v>935</v>
+      </c>
+      <c r="N292" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="O292" t="s" s="2">
+        <v>937</v>
+      </c>
       <c r="P292" t="s" s="2">
         <v>84</v>
       </c>
@@ -42784,31 +42788,29 @@
         <v>84</v>
       </c>
       <c r="AB292" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC292" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="AC292" s="2"/>
       <c r="AD292" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE292" t="s" s="2">
-        <v>84</v>
+        <v>938</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>119</v>
+        <v>939</v>
       </c>
       <c r="AG292" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH292" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI292" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ292" t="s" s="2">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AK292" t="s" s="2">
         <v>84</v>
@@ -42832,10 +42834,10 @@
         <v>84</v>
       </c>
       <c r="AR292" t="s" s="2">
-        <v>84</v>
+        <v>940</v>
       </c>
       <c r="AS292" t="s" s="2">
-        <v>120</v>
+        <v>941</v>
       </c>
       <c r="AT292" t="s" s="2">
         <v>84</v>
@@ -42844,46 +42846,50 @@
         <v>84</v>
       </c>
     </row>
-    <row r="293" hidden="true">
+    <row r="293">
       <c r="A293" t="s" s="2">
-        <v>952</v>
+        <v>942</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>953</v>
-      </c>
-      <c r="C293" s="2"/>
+        <v>933</v>
+      </c>
+      <c r="C293" t="s" s="2">
+        <v>943</v>
+      </c>
       <c r="D293" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E293" s="2"/>
       <c r="F293" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G293" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H293" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I293" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J293" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K293" t="s" s="2">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>124</v>
+        <v>934</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>125</v>
+        <v>935</v>
       </c>
       <c r="N293" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O293" s="2"/>
+        <v>936</v>
+      </c>
+      <c r="O293" t="s" s="2">
+        <v>937</v>
+      </c>
       <c r="P293" t="s" s="2">
         <v>84</v>
       </c>
@@ -42907,31 +42913,29 @@
         <v>84</v>
       </c>
       <c r="X293" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y293" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y293" s="2"/>
       <c r="Z293" t="s" s="2">
-        <v>84</v>
+        <v>944</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB293" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC293" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD293" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE293" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>130</v>
+        <v>939</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>85</v>
@@ -42943,7 +42947,7 @@
         <v>84</v>
       </c>
       <c r="AJ293" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK293" t="s" s="2">
         <v>84</v>
@@ -42967,10 +42971,10 @@
         <v>84</v>
       </c>
       <c r="AR293" t="s" s="2">
-        <v>84</v>
+        <v>940</v>
       </c>
       <c r="AS293" t="s" s="2">
-        <v>120</v>
+        <v>941</v>
       </c>
       <c r="AT293" t="s" s="2">
         <v>84</v>
@@ -42981,12 +42985,14 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="C294" s="2"/>
+        <v>933</v>
+      </c>
+      <c r="C294" t="s" s="2">
+        <v>870</v>
+      </c>
       <c r="D294" t="s" s="2">
         <v>84</v>
       </c>
@@ -43007,18 +43013,20 @@
         <v>103</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>278</v>
+        <v>171</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>956</v>
+        <v>934</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>280</v>
+        <v>935</v>
       </c>
       <c r="N294" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O294" s="2"/>
+        <v>936</v>
+      </c>
+      <c r="O294" t="s" s="2">
+        <v>937</v>
+      </c>
       <c r="P294" t="s" s="2">
         <v>84</v>
       </c>
@@ -43042,13 +43050,11 @@
         <v>84</v>
       </c>
       <c r="X294" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y294" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y294" s="2"/>
       <c r="Z294" t="s" s="2">
-        <v>84</v>
+        <v>946</v>
       </c>
       <c r="AA294" t="s" s="2">
         <v>84</v>
@@ -43066,16 +43072,16 @@
         <v>84</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>282</v>
+        <v>939</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH294" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI294" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ294" t="s" s="2">
         <v>114</v>
@@ -43090,7 +43096,7 @@
         <v>84</v>
       </c>
       <c r="AN294" t="s" s="2">
-        <v>957</v>
+        <v>84</v>
       </c>
       <c r="AO294" t="s" s="2">
         <v>84</v>
@@ -43102,10 +43108,10 @@
         <v>84</v>
       </c>
       <c r="AR294" t="s" s="2">
-        <v>285</v>
+        <v>940</v>
       </c>
       <c r="AS294" t="s" s="2">
-        <v>286</v>
+        <v>941</v>
       </c>
       <c r="AT294" t="s" s="2">
         <v>84</v>
@@ -43114,12 +43120,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>958</v>
+        <v>947</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -43133,7 +43139,7 @@
         <v>102</v>
       </c>
       <c r="H295" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I295" t="s" s="2">
         <v>84</v>
@@ -43142,24 +43148,24 @@
         <v>103</v>
       </c>
       <c r="K295" t="s" s="2">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="L295" t="s" s="2">
-        <v>960</v>
+        <v>949</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>290</v>
+        <v>950</v>
       </c>
       <c r="N295" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O295" s="2"/>
+        <v>951</v>
+      </c>
+      <c r="O295" t="s" s="2">
+        <v>952</v>
+      </c>
       <c r="P295" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q295" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q295" s="2"/>
       <c r="R295" t="s" s="2">
         <v>84</v>
       </c>
@@ -43203,7 +43209,7 @@
         <v>84</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>293</v>
+        <v>953</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>85</v>
@@ -43212,7 +43218,7 @@
         <v>102</v>
       </c>
       <c r="AI295" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ295" t="s" s="2">
         <v>114</v>
@@ -43227,7 +43233,7 @@
         <v>84</v>
       </c>
       <c r="AN295" t="s" s="2">
-        <v>961</v>
+        <v>84</v>
       </c>
       <c r="AO295" t="s" s="2">
         <v>84</v>
@@ -43239,10 +43245,10 @@
         <v>84</v>
       </c>
       <c r="AR295" t="s" s="2">
-        <v>295</v>
+        <v>954</v>
       </c>
       <c r="AS295" t="s" s="2">
-        <v>296</v>
+        <v>955</v>
       </c>
       <c r="AT295" t="s" s="2">
         <v>84</v>
@@ -43253,10 +43259,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -43279,16 +43285,18 @@
         <v>84</v>
       </c>
       <c r="K296" t="s" s="2">
-        <v>963</v>
+        <v>271</v>
       </c>
       <c r="L296" t="s" s="2">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="N296" s="2"/>
-      <c r="O296" s="2"/>
+      <c r="O296" t="s" s="2">
+        <v>862</v>
+      </c>
       <c r="P296" t="s" s="2">
         <v>84</v>
       </c>
@@ -43336,7 +43344,7 @@
         <v>84</v>
       </c>
       <c r="AF296" t="s" s="2">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="AG296" t="s" s="2">
         <v>85</v>
@@ -43360,7 +43368,7 @@
         <v>84</v>
       </c>
       <c r="AN296" t="s" s="2">
-        <v>965</v>
+        <v>84</v>
       </c>
       <c r="AO296" t="s" s="2">
         <v>84</v>
@@ -43375,10 +43383,10 @@
         <v>84</v>
       </c>
       <c r="AS296" t="s" s="2">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="AT296" t="s" s="2">
-        <v>84</v>
+        <v>864</v>
       </c>
       <c r="AU296" t="s" s="2">
         <v>84</v>
@@ -43386,14 +43394,12 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="C297" t="s" s="2">
-        <v>967</v>
-      </c>
+        <v>959</v>
+      </c>
+      <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
         <v>84</v>
       </c>
@@ -43414,13 +43420,13 @@
         <v>84</v>
       </c>
       <c r="K297" t="s" s="2">
-        <v>833</v>
+        <v>116</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>968</v>
+        <v>117</v>
       </c>
       <c r="M297" t="s" s="2">
-        <v>835</v>
+        <v>118</v>
       </c>
       <c r="N297" s="2"/>
       <c r="O297" s="2"/>
@@ -43471,19 +43477,19 @@
         <v>84</v>
       </c>
       <c r="AF297" t="s" s="2">
-        <v>832</v>
+        <v>119</v>
       </c>
       <c r="AG297" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH297" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI297" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ297" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK297" t="s" s="2">
         <v>84</v>
@@ -43507,13 +43513,13 @@
         <v>84</v>
       </c>
       <c r="AR297" t="s" s="2">
-        <v>837</v>
+        <v>84</v>
       </c>
       <c r="AS297" t="s" s="2">
-        <v>838</v>
+        <v>120</v>
       </c>
       <c r="AT297" t="s" s="2">
-        <v>839</v>
+        <v>84</v>
       </c>
       <c r="AU297" t="s" s="2">
         <v>84</v>
@@ -43521,21 +43527,21 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>969</v>
+        <v>960</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>840</v>
+        <v>961</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E298" s="2"/>
       <c r="F298" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G298" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H298" t="s" s="2">
         <v>84</v>
@@ -43547,15 +43553,17 @@
         <v>84</v>
       </c>
       <c r="K298" t="s" s="2">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M298" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N298" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="N298" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="O298" s="2"/>
       <c r="P298" t="s" s="2">
         <v>84</v>
@@ -43592,31 +43600,31 @@
         <v>84</v>
       </c>
       <c r="AB298" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC298" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD298" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE298" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF298" t="s" s="2">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="AG298" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH298" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI298" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ298" t="s" s="2">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="AK298" t="s" s="2">
         <v>84</v>
@@ -43652,44 +43660,44 @@
         <v>84</v>
       </c>
     </row>
-    <row r="299" hidden="true">
+    <row r="299">
       <c r="A299" t="s" s="2">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>841</v>
+        <v>963</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E299" s="2"/>
       <c r="F299" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G299" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H299" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I299" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J299" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K299" t="s" s="2">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>124</v>
+        <v>964</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="N299" t="s" s="2">
-        <v>126</v>
+        <v>281</v>
       </c>
       <c r="O299" s="2"/>
       <c r="P299" t="s" s="2">
@@ -43739,19 +43747,19 @@
         <v>84</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>130</v>
+        <v>282</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH299" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI299" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AJ299" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK299" t="s" s="2">
         <v>84</v>
@@ -43763,7 +43771,7 @@
         <v>84</v>
       </c>
       <c r="AN299" t="s" s="2">
-        <v>84</v>
+        <v>965</v>
       </c>
       <c r="AO299" t="s" s="2">
         <v>84</v>
@@ -43775,10 +43783,10 @@
         <v>84</v>
       </c>
       <c r="AR299" t="s" s="2">
-        <v>84</v>
+        <v>285</v>
       </c>
       <c r="AS299" t="s" s="2">
-        <v>120</v>
+        <v>286</v>
       </c>
       <c r="AT299" t="s" s="2">
         <v>84</v>
@@ -43787,52 +43795,52 @@
         <v>84</v>
       </c>
     </row>
-    <row r="300" hidden="true">
+    <row r="300">
       <c r="A300" t="s" s="2">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>842</v>
+        <v>967</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
-        <v>843</v>
+        <v>84</v>
       </c>
       <c r="E300" s="2"/>
       <c r="F300" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G300" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H300" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I300" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="J300" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>844</v>
+        <v>968</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>845</v>
+        <v>290</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O300" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O300" s="2"/>
       <c r="P300" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q300" s="2"/>
+      <c r="Q300" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="R300" t="s" s="2">
         <v>84</v>
       </c>
@@ -43876,19 +43884,19 @@
         <v>84</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>846</v>
+        <v>293</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH300" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI300" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AJ300" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK300" t="s" s="2">
         <v>84</v>
@@ -43900,7 +43908,7 @@
         <v>84</v>
       </c>
       <c r="AN300" t="s" s="2">
-        <v>84</v>
+        <v>969</v>
       </c>
       <c r="AO300" t="s" s="2">
         <v>84</v>
@@ -43912,10 +43920,10 @@
         <v>84</v>
       </c>
       <c r="AR300" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AS300" t="s" s="2">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="AT300" t="s" s="2">
         <v>84</v>
@@ -43926,10 +43934,10 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
@@ -43940,7 +43948,7 @@
         <v>85</v>
       </c>
       <c r="G301" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H301" t="s" s="2">
         <v>84</v>
@@ -43952,18 +43960,16 @@
         <v>84</v>
       </c>
       <c r="K301" t="s" s="2">
-        <v>488</v>
+        <v>558</v>
       </c>
       <c r="L301" t="s" s="2">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="M301" t="s" s="2">
-        <v>849</v>
+        <v>867</v>
       </c>
       <c r="N301" s="2"/>
-      <c r="O301" t="s" s="2">
-        <v>850</v>
-      </c>
+      <c r="O301" s="2"/>
       <c r="P301" t="s" s="2">
         <v>84</v>
       </c>
@@ -44011,13 +44017,13 @@
         <v>84</v>
       </c>
       <c r="AF301" t="s" s="2">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="AG301" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH301" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI301" t="s" s="2">
         <v>84</v>
@@ -44050,7 +44056,7 @@
         <v>84</v>
       </c>
       <c r="AS301" t="s" s="2">
-        <v>851</v>
+        <v>868</v>
       </c>
       <c r="AT301" t="s" s="2">
         <v>84</v>
@@ -44061,18 +44067,20 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="C302" s="2"/>
+        <v>832</v>
+      </c>
+      <c r="C302" t="s" s="2">
+        <v>972</v>
+      </c>
       <c r="D302" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E302" s="2"/>
       <c r="F302" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G302" t="s" s="2">
         <v>102</v>
@@ -44087,13 +44095,13 @@
         <v>84</v>
       </c>
       <c r="K302" t="s" s="2">
-        <v>251</v>
+        <v>833</v>
       </c>
       <c r="L302" t="s" s="2">
-        <v>853</v>
+        <v>973</v>
       </c>
       <c r="M302" t="s" s="2">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="N302" s="2"/>
       <c r="O302" s="2"/>
@@ -44120,13 +44128,13 @@
         <v>84</v>
       </c>
       <c r="X302" t="s" s="2">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="Y302" t="s" s="2">
-        <v>855</v>
+        <v>84</v>
       </c>
       <c r="Z302" t="s" s="2">
-        <v>856</v>
+        <v>84</v>
       </c>
       <c r="AA302" t="s" s="2">
         <v>84</v>
@@ -44144,13 +44152,13 @@
         <v>84</v>
       </c>
       <c r="AF302" t="s" s="2">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="AG302" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AH302" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI302" t="s" s="2">
         <v>84</v>
@@ -44180,13 +44188,13 @@
         <v>84</v>
       </c>
       <c r="AR302" t="s" s="2">
-        <v>84</v>
+        <v>837</v>
       </c>
       <c r="AS302" t="s" s="2">
         <v>838</v>
       </c>
       <c r="AT302" t="s" s="2">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="AU302" t="s" s="2">
         <v>84</v>
@@ -44197,7 +44205,7 @@
         <v>974</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>921</v>
+        <v>840</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -44330,7 +44338,7 @@
         <v>975</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>923</v>
+        <v>841</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
@@ -44400,16 +44408,16 @@
         <v>84</v>
       </c>
       <c r="AB304" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC304" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD304" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE304" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF304" t="s" s="2">
         <v>130</v>
@@ -44465,11 +44473,11 @@
         <v>976</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>925</v>
+        <v>842</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
-        <v>84</v>
+        <v>843</v>
       </c>
       <c r="E305" s="2"/>
       <c r="F305" t="s" s="2">
@@ -44482,25 +44490,25 @@
         <v>84</v>
       </c>
       <c r="I305" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J305" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K305" t="s" s="2">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="L305" t="s" s="2">
-        <v>926</v>
+        <v>844</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>927</v>
+        <v>845</v>
       </c>
       <c r="N305" t="s" s="2">
-        <v>928</v>
+        <v>126</v>
       </c>
       <c r="O305" t="s" s="2">
-        <v>929</v>
+        <v>485</v>
       </c>
       <c r="P305" t="s" s="2">
         <v>84</v>
@@ -44537,17 +44545,19 @@
         <v>84</v>
       </c>
       <c r="AB305" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AC305" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC305" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD305" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE305" t="s" s="2">
-        <v>930</v>
+        <v>84</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>931</v>
+        <v>846</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>85</v>
@@ -44559,7 +44569,7 @@
         <v>84</v>
       </c>
       <c r="AJ305" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK305" t="s" s="2">
         <v>84</v>
@@ -44583,10 +44593,10 @@
         <v>84</v>
       </c>
       <c r="AR305" t="s" s="2">
-        <v>932</v>
+        <v>84</v>
       </c>
       <c r="AS305" t="s" s="2">
-        <v>933</v>
+        <v>216</v>
       </c>
       <c r="AT305" t="s" s="2">
         <v>84</v>
@@ -44595,16 +44605,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
         <v>977</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="C306" t="s" s="2">
-        <v>978</v>
-      </c>
+        <v>847</v>
+      </c>
+      <c r="C306" s="2"/>
       <c r="D306" t="s" s="2">
         <v>84</v>
       </c>
@@ -44613,31 +44621,29 @@
         <v>85</v>
       </c>
       <c r="G306" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H306" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I306" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J306" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K306" t="s" s="2">
-        <v>171</v>
+        <v>488</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>979</v>
+        <v>848</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="N306" t="s" s="2">
-        <v>928</v>
-      </c>
+        <v>849</v>
+      </c>
+      <c r="N306" s="2"/>
       <c r="O306" t="s" s="2">
-        <v>929</v>
+        <v>850</v>
       </c>
       <c r="P306" t="s" s="2">
         <v>84</v>
@@ -44662,11 +44668,13 @@
         <v>84</v>
       </c>
       <c r="X306" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y306" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y306" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z306" t="s" s="2">
-        <v>980</v>
+        <v>84</v>
       </c>
       <c r="AA306" t="s" s="2">
         <v>84</v>
@@ -44684,7 +44692,7 @@
         <v>84</v>
       </c>
       <c r="AF306" t="s" s="2">
-        <v>931</v>
+        <v>847</v>
       </c>
       <c r="AG306" t="s" s="2">
         <v>85</v>
@@ -44702,7 +44710,7 @@
         <v>84</v>
       </c>
       <c r="AL306" t="s" s="2">
-        <v>981</v>
+        <v>84</v>
       </c>
       <c r="AM306" t="s" s="2">
         <v>84</v>
@@ -44720,10 +44728,10 @@
         <v>84</v>
       </c>
       <c r="AR306" t="s" s="2">
-        <v>932</v>
+        <v>84</v>
       </c>
       <c r="AS306" t="s" s="2">
-        <v>933</v>
+        <v>851</v>
       </c>
       <c r="AT306" t="s" s="2">
         <v>84</v>
@@ -44732,50 +44740,44 @@
         <v>84</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="C307" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>852</v>
+      </c>
+      <c r="C307" s="2"/>
       <c r="D307" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E307" s="2"/>
       <c r="F307" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G307" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H307" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I307" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J307" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K307" t="s" s="2">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="L307" t="s" s="2">
-        <v>983</v>
+        <v>853</v>
       </c>
       <c r="M307" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="N307" t="s" s="2">
-        <v>928</v>
-      </c>
-      <c r="O307" t="s" s="2">
-        <v>929</v>
-      </c>
+        <v>854</v>
+      </c>
+      <c r="N307" s="2"/>
+      <c r="O307" s="2"/>
       <c r="P307" t="s" s="2">
         <v>84</v>
       </c>
@@ -44799,11 +44801,13 @@
         <v>84</v>
       </c>
       <c r="X307" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y307" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="Y307" t="s" s="2">
+        <v>855</v>
+      </c>
       <c r="Z307" t="s" s="2">
-        <v>984</v>
+        <v>856</v>
       </c>
       <c r="AA307" t="s" s="2">
         <v>84</v>
@@ -44821,13 +44825,13 @@
         <v>84</v>
       </c>
       <c r="AF307" t="s" s="2">
-        <v>931</v>
+        <v>852</v>
       </c>
       <c r="AG307" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH307" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI307" t="s" s="2">
         <v>84</v>
@@ -44839,7 +44843,7 @@
         <v>84</v>
       </c>
       <c r="AL307" t="s" s="2">
-        <v>985</v>
+        <v>84</v>
       </c>
       <c r="AM307" t="s" s="2">
         <v>84</v>
@@ -44857,13 +44861,13 @@
         <v>84</v>
       </c>
       <c r="AR307" t="s" s="2">
-        <v>932</v>
+        <v>84</v>
       </c>
       <c r="AS307" t="s" s="2">
-        <v>933</v>
+        <v>838</v>
       </c>
       <c r="AT307" t="s" s="2">
-        <v>84</v>
+        <v>858</v>
       </c>
       <c r="AU307" t="s" s="2">
         <v>84</v>
@@ -44871,10 +44875,10 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" t="s" s="2">
@@ -44894,23 +44898,19 @@
         <v>84</v>
       </c>
       <c r="J308" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K308" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L308" t="s" s="2">
-        <v>941</v>
+        <v>117</v>
       </c>
       <c r="M308" t="s" s="2">
-        <v>942</v>
-      </c>
-      <c r="N308" t="s" s="2">
-        <v>943</v>
-      </c>
-      <c r="O308" t="s" s="2">
-        <v>944</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N308" s="2"/>
+      <c r="O308" s="2"/>
       <c r="P308" t="s" s="2">
         <v>84</v>
       </c>
@@ -44958,7 +44958,7 @@
         <v>84</v>
       </c>
       <c r="AF308" t="s" s="2">
-        <v>945</v>
+        <v>119</v>
       </c>
       <c r="AG308" t="s" s="2">
         <v>85</v>
@@ -44970,7 +44970,7 @@
         <v>84</v>
       </c>
       <c r="AJ308" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK308" t="s" s="2">
         <v>84</v>
@@ -44994,10 +44994,10 @@
         <v>84</v>
       </c>
       <c r="AR308" t="s" s="2">
-        <v>946</v>
+        <v>84</v>
       </c>
       <c r="AS308" t="s" s="2">
-        <v>947</v>
+        <v>120</v>
       </c>
       <c r="AT308" t="s" s="2">
         <v>84</v>
@@ -45006,26 +45006,26 @@
         <v>84</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>859</v>
+        <v>931</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E309" s="2"/>
       <c r="F309" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G309" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H309" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I309" t="s" s="2">
         <v>84</v>
@@ -45034,18 +45034,18 @@
         <v>84</v>
       </c>
       <c r="K309" t="s" s="2">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="L309" t="s" s="2">
-        <v>860</v>
+        <v>124</v>
       </c>
       <c r="M309" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="N309" s="2"/>
-      <c r="O309" t="s" s="2">
-        <v>862</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N309" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O309" s="2"/>
       <c r="P309" t="s" s="2">
         <v>84</v>
       </c>
@@ -45081,31 +45081,31 @@
         <v>84</v>
       </c>
       <c r="AB309" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC309" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD309" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE309" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF309" t="s" s="2">
-        <v>859</v>
+        <v>130</v>
       </c>
       <c r="AG309" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH309" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI309" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ309" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK309" t="s" s="2">
         <v>84</v>
@@ -45132,10 +45132,10 @@
         <v>84</v>
       </c>
       <c r="AS309" t="s" s="2">
-        <v>863</v>
+        <v>120</v>
       </c>
       <c r="AT309" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AU309" t="s" s="2">
         <v>84</v>
@@ -45143,10 +45143,10 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>951</v>
+        <v>933</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" t="s" s="2">
@@ -45157,7 +45157,7 @@
         <v>85</v>
       </c>
       <c r="G310" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H310" t="s" s="2">
         <v>84</v>
@@ -45166,19 +45166,23 @@
         <v>84</v>
       </c>
       <c r="J310" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K310" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="L310" t="s" s="2">
-        <v>117</v>
+        <v>934</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N310" s="2"/>
-      <c r="O310" s="2"/>
+        <v>935</v>
+      </c>
+      <c r="N310" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="O310" t="s" s="2">
+        <v>937</v>
+      </c>
       <c r="P310" t="s" s="2">
         <v>84</v>
       </c>
@@ -45214,31 +45218,29 @@
         <v>84</v>
       </c>
       <c r="AB310" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC310" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="AC310" s="2"/>
       <c r="AD310" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE310" t="s" s="2">
-        <v>84</v>
+        <v>938</v>
       </c>
       <c r="AF310" t="s" s="2">
-        <v>119</v>
+        <v>939</v>
       </c>
       <c r="AG310" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH310" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI310" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ310" t="s" s="2">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AK310" t="s" s="2">
         <v>84</v>
@@ -45262,10 +45264,10 @@
         <v>84</v>
       </c>
       <c r="AR310" t="s" s="2">
-        <v>84</v>
+        <v>940</v>
       </c>
       <c r="AS310" t="s" s="2">
-        <v>120</v>
+        <v>941</v>
       </c>
       <c r="AT310" t="s" s="2">
         <v>84</v>
@@ -45274,46 +45276,50 @@
         <v>84</v>
       </c>
     </row>
-    <row r="311" hidden="true">
+    <row r="311">
       <c r="A311" t="s" s="2">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>953</v>
-      </c>
-      <c r="C311" s="2"/>
+        <v>933</v>
+      </c>
+      <c r="C311" t="s" s="2">
+        <v>983</v>
+      </c>
       <c r="D311" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E311" s="2"/>
       <c r="F311" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G311" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H311" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I311" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J311" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K311" t="s" s="2">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>124</v>
+        <v>984</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>125</v>
+        <v>935</v>
       </c>
       <c r="N311" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O311" s="2"/>
+        <v>936</v>
+      </c>
+      <c r="O311" t="s" s="2">
+        <v>937</v>
+      </c>
       <c r="P311" t="s" s="2">
         <v>84</v>
       </c>
@@ -45337,31 +45343,29 @@
         <v>84</v>
       </c>
       <c r="X311" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y311" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y311" s="2"/>
       <c r="Z311" t="s" s="2">
-        <v>84</v>
+        <v>985</v>
       </c>
       <c r="AA311" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB311" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC311" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD311" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE311" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF311" t="s" s="2">
-        <v>130</v>
+        <v>939</v>
       </c>
       <c r="AG311" t="s" s="2">
         <v>85</v>
@@ -45373,13 +45377,13 @@
         <v>84</v>
       </c>
       <c r="AJ311" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK311" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL311" t="s" s="2">
-        <v>84</v>
+        <v>986</v>
       </c>
       <c r="AM311" t="s" s="2">
         <v>84</v>
@@ -45397,10 +45401,10 @@
         <v>84</v>
       </c>
       <c r="AR311" t="s" s="2">
-        <v>84</v>
+        <v>940</v>
       </c>
       <c r="AS311" t="s" s="2">
-        <v>120</v>
+        <v>941</v>
       </c>
       <c r="AT311" t="s" s="2">
         <v>84</v>
@@ -45409,14 +45413,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="312" hidden="true">
+    <row r="312">
       <c r="A312" t="s" s="2">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="C312" s="2"/>
+        <v>933</v>
+      </c>
+      <c r="C312" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="D312" t="s" s="2">
         <v>84</v>
       </c>
@@ -45428,7 +45434,7 @@
         <v>102</v>
       </c>
       <c r="H312" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I312" t="s" s="2">
         <v>84</v>
@@ -45437,18 +45443,20 @@
         <v>103</v>
       </c>
       <c r="K312" t="s" s="2">
-        <v>278</v>
+        <v>171</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>280</v>
+        <v>935</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O312" s="2"/>
+        <v>936</v>
+      </c>
+      <c r="O312" t="s" s="2">
+        <v>937</v>
+      </c>
       <c r="P312" t="s" s="2">
         <v>84</v>
       </c>
@@ -45472,13 +45480,11 @@
         <v>84</v>
       </c>
       <c r="X312" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y312" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y312" s="2"/>
       <c r="Z312" t="s" s="2">
-        <v>84</v>
+        <v>989</v>
       </c>
       <c r="AA312" t="s" s="2">
         <v>84</v>
@@ -45496,16 +45502,16 @@
         <v>84</v>
       </c>
       <c r="AF312" t="s" s="2">
-        <v>282</v>
+        <v>939</v>
       </c>
       <c r="AG312" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH312" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI312" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ312" t="s" s="2">
         <v>114</v>
@@ -45514,7 +45520,7 @@
         <v>84</v>
       </c>
       <c r="AL312" t="s" s="2">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="AM312" t="s" s="2">
         <v>84</v>
@@ -45532,10 +45538,10 @@
         <v>84</v>
       </c>
       <c r="AR312" t="s" s="2">
-        <v>285</v>
+        <v>940</v>
       </c>
       <c r="AS312" t="s" s="2">
-        <v>286</v>
+        <v>941</v>
       </c>
       <c r="AT312" t="s" s="2">
         <v>84</v>
@@ -45546,10 +45552,10 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" t="s" s="2">
@@ -45572,24 +45578,24 @@
         <v>103</v>
       </c>
       <c r="K313" t="s" s="2">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>994</v>
+        <v>949</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>290</v>
+        <v>950</v>
       </c>
       <c r="N313" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O313" s="2"/>
+        <v>951</v>
+      </c>
+      <c r="O313" t="s" s="2">
+        <v>952</v>
+      </c>
       <c r="P313" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q313" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q313" s="2"/>
       <c r="R313" t="s" s="2">
         <v>84</v>
       </c>
@@ -45633,7 +45639,7 @@
         <v>84</v>
       </c>
       <c r="AF313" t="s" s="2">
-        <v>293</v>
+        <v>953</v>
       </c>
       <c r="AG313" t="s" s="2">
         <v>85</v>
@@ -45642,7 +45648,7 @@
         <v>102</v>
       </c>
       <c r="AI313" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ313" t="s" s="2">
         <v>114</v>
@@ -45651,7 +45657,7 @@
         <v>84</v>
       </c>
       <c r="AL313" t="s" s="2">
-        <v>995</v>
+        <v>84</v>
       </c>
       <c r="AM313" t="s" s="2">
         <v>84</v>
@@ -45669,10 +45675,10 @@
         <v>84</v>
       </c>
       <c r="AR313" t="s" s="2">
-        <v>295</v>
+        <v>954</v>
       </c>
       <c r="AS313" t="s" s="2">
-        <v>296</v>
+        <v>955</v>
       </c>
       <c r="AT313" t="s" s="2">
         <v>84</v>
@@ -45681,12 +45687,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="314" hidden="true">
+    <row r="314">
       <c r="A314" t="s" s="2">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" t="s" s="2">
@@ -45700,7 +45706,7 @@
         <v>102</v>
       </c>
       <c r="H314" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I314" t="s" s="2">
         <v>84</v>
@@ -45709,16 +45715,18 @@
         <v>84</v>
       </c>
       <c r="K314" t="s" s="2">
-        <v>558</v>
+        <v>271</v>
       </c>
       <c r="L314" t="s" s="2">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="M314" t="s" s="2">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="N314" s="2"/>
-      <c r="O314" s="2"/>
+      <c r="O314" t="s" s="2">
+        <v>862</v>
+      </c>
       <c r="P314" t="s" s="2">
         <v>84</v>
       </c>
@@ -45766,7 +45774,7 @@
         <v>84</v>
       </c>
       <c r="AF314" t="s" s="2">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="AG314" t="s" s="2">
         <v>85</v>
@@ -45805,10 +45813,10 @@
         <v>84</v>
       </c>
       <c r="AS314" t="s" s="2">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="AT314" t="s" s="2">
-        <v>84</v>
+        <v>864</v>
       </c>
       <c r="AU314" t="s" s="2">
         <v>84</v>
@@ -45816,14 +45824,12 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="C315" t="s" s="2">
-        <v>998</v>
-      </c>
+        <v>959</v>
+      </c>
+      <c r="C315" s="2"/>
       <c r="D315" t="s" s="2">
         <v>84</v>
       </c>
@@ -45832,7 +45838,7 @@
         <v>85</v>
       </c>
       <c r="G315" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H315" t="s" s="2">
         <v>84</v>
@@ -45844,13 +45850,13 @@
         <v>84</v>
       </c>
       <c r="K315" t="s" s="2">
-        <v>833</v>
+        <v>116</v>
       </c>
       <c r="L315" t="s" s="2">
-        <v>999</v>
+        <v>117</v>
       </c>
       <c r="M315" t="s" s="2">
-        <v>835</v>
+        <v>118</v>
       </c>
       <c r="N315" s="2"/>
       <c r="O315" s="2"/>
@@ -45901,19 +45907,19 @@
         <v>84</v>
       </c>
       <c r="AF315" t="s" s="2">
-        <v>832</v>
+        <v>119</v>
       </c>
       <c r="AG315" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH315" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI315" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ315" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK315" t="s" s="2">
         <v>84</v>
@@ -45937,13 +45943,13 @@
         <v>84</v>
       </c>
       <c r="AR315" t="s" s="2">
-        <v>837</v>
+        <v>84</v>
       </c>
       <c r="AS315" t="s" s="2">
-        <v>838</v>
+        <v>120</v>
       </c>
       <c r="AT315" t="s" s="2">
-        <v>839</v>
+        <v>84</v>
       </c>
       <c r="AU315" t="s" s="2">
         <v>84</v>
@@ -45951,21 +45957,21 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>840</v>
+        <v>961</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E316" s="2"/>
       <c r="F316" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G316" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H316" t="s" s="2">
         <v>84</v>
@@ -45977,15 +45983,17 @@
         <v>84</v>
       </c>
       <c r="K316" t="s" s="2">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L316" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M316" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N316" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="N316" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="O316" s="2"/>
       <c r="P316" t="s" s="2">
         <v>84</v>
@@ -46022,31 +46030,31 @@
         <v>84</v>
       </c>
       <c r="AB316" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC316" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD316" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE316" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF316" t="s" s="2">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="AG316" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH316" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI316" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ316" t="s" s="2">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="AK316" t="s" s="2">
         <v>84</v>
@@ -46084,21 +46092,21 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>841</v>
+        <v>963</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E317" s="2"/>
       <c r="F317" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G317" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H317" t="s" s="2">
         <v>84</v>
@@ -46107,19 +46115,19 @@
         <v>84</v>
       </c>
       <c r="J317" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K317" t="s" s="2">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="L317" t="s" s="2">
-        <v>124</v>
+        <v>996</v>
       </c>
       <c r="M317" t="s" s="2">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="N317" t="s" s="2">
-        <v>126</v>
+        <v>281</v>
       </c>
       <c r="O317" s="2"/>
       <c r="P317" t="s" s="2">
@@ -46169,25 +46177,25 @@
         <v>84</v>
       </c>
       <c r="AF317" t="s" s="2">
-        <v>130</v>
+        <v>282</v>
       </c>
       <c r="AG317" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH317" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI317" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AJ317" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK317" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL317" t="s" s="2">
-        <v>84</v>
+        <v>997</v>
       </c>
       <c r="AM317" t="s" s="2">
         <v>84</v>
@@ -46205,10 +46213,10 @@
         <v>84</v>
       </c>
       <c r="AR317" t="s" s="2">
-        <v>84</v>
+        <v>285</v>
       </c>
       <c r="AS317" t="s" s="2">
-        <v>120</v>
+        <v>286</v>
       </c>
       <c r="AT317" t="s" s="2">
         <v>84</v>
@@ -46219,50 +46227,50 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>842</v>
+        <v>967</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" t="s" s="2">
-        <v>843</v>
+        <v>84</v>
       </c>
       <c r="E318" s="2"/>
       <c r="F318" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G318" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H318" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I318" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="J318" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K318" t="s" s="2">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="L318" t="s" s="2">
-        <v>844</v>
+        <v>999</v>
       </c>
       <c r="M318" t="s" s="2">
-        <v>845</v>
+        <v>290</v>
       </c>
       <c r="N318" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O318" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O318" s="2"/>
       <c r="P318" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q318" s="2"/>
+      <c r="Q318" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="R318" t="s" s="2">
         <v>84</v>
       </c>
@@ -46306,25 +46314,25 @@
         <v>84</v>
       </c>
       <c r="AF318" t="s" s="2">
-        <v>846</v>
+        <v>293</v>
       </c>
       <c r="AG318" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH318" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI318" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AJ318" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK318" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL318" t="s" s="2">
-        <v>84</v>
+        <v>1000</v>
       </c>
       <c r="AM318" t="s" s="2">
         <v>84</v>
@@ -46342,10 +46350,10 @@
         <v>84</v>
       </c>
       <c r="AR318" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AS318" t="s" s="2">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="AT318" t="s" s="2">
         <v>84</v>
@@ -46356,10 +46364,10 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" t="s" s="2">
@@ -46370,7 +46378,7 @@
         <v>85</v>
       </c>
       <c r="G319" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H319" t="s" s="2">
         <v>84</v>
@@ -46382,18 +46390,16 @@
         <v>84</v>
       </c>
       <c r="K319" t="s" s="2">
-        <v>488</v>
+        <v>558</v>
       </c>
       <c r="L319" t="s" s="2">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="M319" t="s" s="2">
-        <v>849</v>
+        <v>867</v>
       </c>
       <c r="N319" s="2"/>
-      <c r="O319" t="s" s="2">
-        <v>850</v>
-      </c>
+      <c r="O319" s="2"/>
       <c r="P319" t="s" s="2">
         <v>84</v>
       </c>
@@ -46441,13 +46447,13 @@
         <v>84</v>
       </c>
       <c r="AF319" t="s" s="2">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="AG319" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH319" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI319" t="s" s="2">
         <v>84</v>
@@ -46480,7 +46486,7 @@
         <v>84</v>
       </c>
       <c r="AS319" t="s" s="2">
-        <v>851</v>
+        <v>868</v>
       </c>
       <c r="AT319" t="s" s="2">
         <v>84</v>
@@ -46491,21 +46497,23 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="C320" s="2"/>
+        <v>832</v>
+      </c>
+      <c r="C320" t="s" s="2">
+        <v>1003</v>
+      </c>
       <c r="D320" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E320" s="2"/>
       <c r="F320" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G320" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H320" t="s" s="2">
         <v>84</v>
@@ -46517,13 +46525,13 @@
         <v>84</v>
       </c>
       <c r="K320" t="s" s="2">
-        <v>251</v>
+        <v>833</v>
       </c>
       <c r="L320" t="s" s="2">
-        <v>853</v>
+        <v>1004</v>
       </c>
       <c r="M320" t="s" s="2">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="N320" s="2"/>
       <c r="O320" s="2"/>
@@ -46550,13 +46558,13 @@
         <v>84</v>
       </c>
       <c r="X320" t="s" s="2">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="Y320" t="s" s="2">
-        <v>855</v>
+        <v>84</v>
       </c>
       <c r="Z320" t="s" s="2">
-        <v>856</v>
+        <v>84</v>
       </c>
       <c r="AA320" t="s" s="2">
         <v>84</v>
@@ -46574,13 +46582,13 @@
         <v>84</v>
       </c>
       <c r="AF320" t="s" s="2">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="AG320" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AH320" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI320" t="s" s="2">
         <v>84</v>
@@ -46589,7 +46597,7 @@
         <v>114</v>
       </c>
       <c r="AK320" t="s" s="2">
-        <v>1005</v>
+        <v>84</v>
       </c>
       <c r="AL320" t="s" s="2">
         <v>84</v>
@@ -46610,13 +46618,13 @@
         <v>84</v>
       </c>
       <c r="AR320" t="s" s="2">
-        <v>84</v>
+        <v>837</v>
       </c>
       <c r="AS320" t="s" s="2">
         <v>838</v>
       </c>
       <c r="AT320" t="s" s="2">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="AU320" t="s" s="2">
         <v>84</v>
@@ -46624,10 +46632,10 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>921</v>
+        <v>840</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" t="s" s="2">
@@ -46757,10 +46765,10 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>923</v>
+        <v>841</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" t="s" s="2">
@@ -46830,16 +46838,16 @@
         <v>84</v>
       </c>
       <c r="AB322" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC322" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD322" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE322" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF322" t="s" s="2">
         <v>130</v>
@@ -46892,14 +46900,14 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>925</v>
+        <v>842</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" t="s" s="2">
-        <v>84</v>
+        <v>843</v>
       </c>
       <c r="E323" s="2"/>
       <c r="F323" t="s" s="2">
@@ -46912,25 +46920,25 @@
         <v>84</v>
       </c>
       <c r="I323" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J323" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K323" t="s" s="2">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="L323" t="s" s="2">
-        <v>926</v>
+        <v>844</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>927</v>
+        <v>845</v>
       </c>
       <c r="N323" t="s" s="2">
-        <v>928</v>
+        <v>126</v>
       </c>
       <c r="O323" t="s" s="2">
-        <v>929</v>
+        <v>485</v>
       </c>
       <c r="P323" t="s" s="2">
         <v>84</v>
@@ -46967,17 +46975,19 @@
         <v>84</v>
       </c>
       <c r="AB323" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AC323" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC323" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD323" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE323" t="s" s="2">
-        <v>930</v>
+        <v>84</v>
       </c>
       <c r="AF323" t="s" s="2">
-        <v>931</v>
+        <v>846</v>
       </c>
       <c r="AG323" t="s" s="2">
         <v>85</v>
@@ -46989,7 +46999,7 @@
         <v>84</v>
       </c>
       <c r="AJ323" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK323" t="s" s="2">
         <v>84</v>
@@ -47013,10 +47023,10 @@
         <v>84</v>
       </c>
       <c r="AR323" t="s" s="2">
-        <v>932</v>
+        <v>84</v>
       </c>
       <c r="AS323" t="s" s="2">
-        <v>933</v>
+        <v>216</v>
       </c>
       <c r="AT323" t="s" s="2">
         <v>84</v>
@@ -47025,16 +47035,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="C324" t="s" s="2">
-        <v>1010</v>
-      </c>
+        <v>847</v>
+      </c>
+      <c r="C324" s="2"/>
       <c r="D324" t="s" s="2">
         <v>84</v>
       </c>
@@ -47043,31 +47051,29 @@
         <v>85</v>
       </c>
       <c r="G324" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H324" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I324" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J324" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K324" t="s" s="2">
-        <v>171</v>
+        <v>488</v>
       </c>
       <c r="L324" t="s" s="2">
-        <v>1011</v>
+        <v>848</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="N324" t="s" s="2">
-        <v>928</v>
-      </c>
+        <v>849</v>
+      </c>
+      <c r="N324" s="2"/>
       <c r="O324" t="s" s="2">
-        <v>929</v>
+        <v>850</v>
       </c>
       <c r="P324" t="s" s="2">
         <v>84</v>
@@ -47092,11 +47098,13 @@
         <v>84</v>
       </c>
       <c r="X324" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y324" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y324" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z324" t="s" s="2">
-        <v>1012</v>
+        <v>84</v>
       </c>
       <c r="AA324" t="s" s="2">
         <v>84</v>
@@ -47114,7 +47122,7 @@
         <v>84</v>
       </c>
       <c r="AF324" t="s" s="2">
-        <v>931</v>
+        <v>847</v>
       </c>
       <c r="AG324" t="s" s="2">
         <v>85</v>
@@ -47129,7 +47137,7 @@
         <v>114</v>
       </c>
       <c r="AK324" t="s" s="2">
-        <v>1013</v>
+        <v>84</v>
       </c>
       <c r="AL324" t="s" s="2">
         <v>84</v>
@@ -47150,10 +47158,10 @@
         <v>84</v>
       </c>
       <c r="AR324" t="s" s="2">
-        <v>932</v>
+        <v>84</v>
       </c>
       <c r="AS324" t="s" s="2">
-        <v>933</v>
+        <v>851</v>
       </c>
       <c r="AT324" t="s" s="2">
         <v>84</v>
@@ -47162,50 +47170,44 @@
         <v>84</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" hidden="true">
       <c r="A325" t="s" s="2">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="C325" t="s" s="2">
-        <v>998</v>
-      </c>
+        <v>852</v>
+      </c>
+      <c r="C325" s="2"/>
       <c r="D325" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E325" s="2"/>
       <c r="F325" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G325" t="s" s="2">
         <v>102</v>
       </c>
       <c r="H325" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I325" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J325" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K325" t="s" s="2">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="L325" t="s" s="2">
-        <v>1015</v>
+        <v>853</v>
       </c>
       <c r="M325" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="N325" t="s" s="2">
-        <v>928</v>
-      </c>
-      <c r="O325" t="s" s="2">
-        <v>929</v>
-      </c>
+        <v>854</v>
+      </c>
+      <c r="N325" s="2"/>
+      <c r="O325" s="2"/>
       <c r="P325" t="s" s="2">
         <v>84</v>
       </c>
@@ -47229,11 +47231,13 @@
         <v>84</v>
       </c>
       <c r="X325" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y325" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="Y325" t="s" s="2">
+        <v>855</v>
+      </c>
       <c r="Z325" t="s" s="2">
-        <v>1016</v>
+        <v>856</v>
       </c>
       <c r="AA325" t="s" s="2">
         <v>84</v>
@@ -47251,13 +47255,13 @@
         <v>84</v>
       </c>
       <c r="AF325" t="s" s="2">
-        <v>931</v>
+        <v>852</v>
       </c>
       <c r="AG325" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH325" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI325" t="s" s="2">
         <v>84</v>
@@ -47266,7 +47270,7 @@
         <v>114</v>
       </c>
       <c r="AK325" t="s" s="2">
-        <v>84</v>
+        <v>1010</v>
       </c>
       <c r="AL325" t="s" s="2">
         <v>84</v>
@@ -47287,13 +47291,13 @@
         <v>84</v>
       </c>
       <c r="AR325" t="s" s="2">
-        <v>932</v>
+        <v>84</v>
       </c>
       <c r="AS325" t="s" s="2">
-        <v>933</v>
+        <v>838</v>
       </c>
       <c r="AT325" t="s" s="2">
-        <v>84</v>
+        <v>858</v>
       </c>
       <c r="AU325" t="s" s="2">
         <v>84</v>
@@ -47301,10 +47305,10 @@
     </row>
     <row r="326" hidden="true">
       <c r="A326" t="s" s="2">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" t="s" s="2">
@@ -47324,23 +47328,19 @@
         <v>84</v>
       </c>
       <c r="J326" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K326" t="s" s="2">
         <v>116</v>
       </c>
       <c r="L326" t="s" s="2">
-        <v>941</v>
+        <v>117</v>
       </c>
       <c r="M326" t="s" s="2">
-        <v>942</v>
-      </c>
-      <c r="N326" t="s" s="2">
-        <v>943</v>
-      </c>
-      <c r="O326" t="s" s="2">
-        <v>944</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N326" s="2"/>
+      <c r="O326" s="2"/>
       <c r="P326" t="s" s="2">
         <v>84</v>
       </c>
@@ -47388,7 +47388,7 @@
         <v>84</v>
       </c>
       <c r="AF326" t="s" s="2">
-        <v>945</v>
+        <v>119</v>
       </c>
       <c r="AG326" t="s" s="2">
         <v>85</v>
@@ -47400,7 +47400,7 @@
         <v>84</v>
       </c>
       <c r="AJ326" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK326" t="s" s="2">
         <v>84</v>
@@ -47424,10 +47424,10 @@
         <v>84</v>
       </c>
       <c r="AR326" t="s" s="2">
-        <v>946</v>
+        <v>84</v>
       </c>
       <c r="AS326" t="s" s="2">
-        <v>947</v>
+        <v>120</v>
       </c>
       <c r="AT326" t="s" s="2">
         <v>84</v>
@@ -47438,21 +47438,21 @@
     </row>
     <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>859</v>
+        <v>931</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E327" s="2"/>
       <c r="F327" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G327" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H327" t="s" s="2">
         <v>84</v>
@@ -47464,18 +47464,18 @@
         <v>84</v>
       </c>
       <c r="K327" t="s" s="2">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="L327" t="s" s="2">
-        <v>860</v>
+        <v>124</v>
       </c>
       <c r="M327" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="N327" s="2"/>
-      <c r="O327" t="s" s="2">
-        <v>862</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="N327" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O327" s="2"/>
       <c r="P327" t="s" s="2">
         <v>84</v>
       </c>
@@ -47511,31 +47511,31 @@
         <v>84</v>
       </c>
       <c r="AB327" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC327" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD327" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE327" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF327" t="s" s="2">
-        <v>859</v>
+        <v>130</v>
       </c>
       <c r="AG327" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH327" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI327" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ327" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK327" t="s" s="2">
         <v>84</v>
@@ -47562,10 +47562,10 @@
         <v>84</v>
       </c>
       <c r="AS327" t="s" s="2">
-        <v>863</v>
+        <v>120</v>
       </c>
       <c r="AT327" t="s" s="2">
-        <v>864</v>
+        <v>84</v>
       </c>
       <c r="AU327" t="s" s="2">
         <v>84</v>
@@ -47573,10 +47573,10 @@
     </row>
     <row r="328" hidden="true">
       <c r="A328" t="s" s="2">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>951</v>
+        <v>933</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" t="s" s="2">
@@ -47587,7 +47587,7 @@
         <v>85</v>
       </c>
       <c r="G328" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H328" t="s" s="2">
         <v>84</v>
@@ -47596,19 +47596,23 @@
         <v>84</v>
       </c>
       <c r="J328" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K328" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="L328" t="s" s="2">
-        <v>117</v>
+        <v>934</v>
       </c>
       <c r="M328" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N328" s="2"/>
-      <c r="O328" s="2"/>
+        <v>935</v>
+      </c>
+      <c r="N328" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="O328" t="s" s="2">
+        <v>937</v>
+      </c>
       <c r="P328" t="s" s="2">
         <v>84</v>
       </c>
@@ -47644,31 +47648,29 @@
         <v>84</v>
       </c>
       <c r="AB328" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC328" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="AC328" s="2"/>
       <c r="AD328" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE328" t="s" s="2">
-        <v>84</v>
+        <v>938</v>
       </c>
       <c r="AF328" t="s" s="2">
-        <v>119</v>
+        <v>939</v>
       </c>
       <c r="AG328" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH328" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI328" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ328" t="s" s="2">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="AK328" t="s" s="2">
         <v>84</v>
@@ -47692,10 +47694,10 @@
         <v>84</v>
       </c>
       <c r="AR328" t="s" s="2">
-        <v>84</v>
+        <v>940</v>
       </c>
       <c r="AS328" t="s" s="2">
-        <v>120</v>
+        <v>941</v>
       </c>
       <c r="AT328" t="s" s="2">
         <v>84</v>
@@ -47704,46 +47706,50 @@
         <v>84</v>
       </c>
     </row>
-    <row r="329" hidden="true">
+    <row r="329">
       <c r="A329" t="s" s="2">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>953</v>
-      </c>
-      <c r="C329" s="2"/>
+        <v>933</v>
+      </c>
+      <c r="C329" t="s" s="2">
+        <v>1015</v>
+      </c>
       <c r="D329" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E329" s="2"/>
       <c r="F329" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G329" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H329" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I329" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J329" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K329" t="s" s="2">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="L329" t="s" s="2">
-        <v>124</v>
+        <v>1016</v>
       </c>
       <c r="M329" t="s" s="2">
-        <v>125</v>
+        <v>935</v>
       </c>
       <c r="N329" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O329" s="2"/>
+        <v>936</v>
+      </c>
+      <c r="O329" t="s" s="2">
+        <v>937</v>
+      </c>
       <c r="P329" t="s" s="2">
         <v>84</v>
       </c>
@@ -47767,31 +47773,29 @@
         <v>84</v>
       </c>
       <c r="X329" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y329" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y329" s="2"/>
       <c r="Z329" t="s" s="2">
-        <v>84</v>
+        <v>1017</v>
       </c>
       <c r="AA329" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB329" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC329" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD329" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE329" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF329" t="s" s="2">
-        <v>130</v>
+        <v>939</v>
       </c>
       <c r="AG329" t="s" s="2">
         <v>85</v>
@@ -47803,10 +47807,10 @@
         <v>84</v>
       </c>
       <c r="AJ329" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK329" t="s" s="2">
-        <v>84</v>
+        <v>1018</v>
       </c>
       <c r="AL329" t="s" s="2">
         <v>84</v>
@@ -47827,10 +47831,10 @@
         <v>84</v>
       </c>
       <c r="AR329" t="s" s="2">
-        <v>84</v>
+        <v>940</v>
       </c>
       <c r="AS329" t="s" s="2">
-        <v>120</v>
+        <v>941</v>
       </c>
       <c r="AT329" t="s" s="2">
         <v>84</v>
@@ -47839,14 +47843,16 @@
         <v>84</v>
       </c>
     </row>
-    <row r="330" hidden="true">
+    <row r="330">
       <c r="A330" t="s" s="2">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="C330" s="2"/>
+        <v>933</v>
+      </c>
+      <c r="C330" t="s" s="2">
+        <v>1003</v>
+      </c>
       <c r="D330" t="s" s="2">
         <v>84</v>
       </c>
@@ -47858,7 +47864,7 @@
         <v>102</v>
       </c>
       <c r="H330" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I330" t="s" s="2">
         <v>84</v>
@@ -47867,18 +47873,20 @@
         <v>103</v>
       </c>
       <c r="K330" t="s" s="2">
-        <v>278</v>
+        <v>171</v>
       </c>
       <c r="L330" t="s" s="2">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>280</v>
+        <v>935</v>
       </c>
       <c r="N330" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O330" s="2"/>
+        <v>936</v>
+      </c>
+      <c r="O330" t="s" s="2">
+        <v>937</v>
+      </c>
       <c r="P330" t="s" s="2">
         <v>84</v>
       </c>
@@ -47902,13 +47910,11 @@
         <v>84</v>
       </c>
       <c r="X330" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y330" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y330" s="2"/>
       <c r="Z330" t="s" s="2">
-        <v>84</v>
+        <v>1021</v>
       </c>
       <c r="AA330" t="s" s="2">
         <v>84</v>
@@ -47926,22 +47932,22 @@
         <v>84</v>
       </c>
       <c r="AF330" t="s" s="2">
-        <v>282</v>
+        <v>939</v>
       </c>
       <c r="AG330" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH330" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI330" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ330" t="s" s="2">
         <v>114</v>
       </c>
       <c r="AK330" t="s" s="2">
-        <v>1023</v>
+        <v>84</v>
       </c>
       <c r="AL330" t="s" s="2">
         <v>84</v>
@@ -47962,10 +47968,10 @@
         <v>84</v>
       </c>
       <c r="AR330" t="s" s="2">
-        <v>285</v>
+        <v>940</v>
       </c>
       <c r="AS330" t="s" s="2">
-        <v>286</v>
+        <v>941</v>
       </c>
       <c r="AT330" t="s" s="2">
         <v>84</v>
@@ -47976,10 +47982,10 @@
     </row>
     <row r="331" hidden="true">
       <c r="A331" t="s" s="2">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" t="s" s="2">
@@ -48002,24 +48008,24 @@
         <v>103</v>
       </c>
       <c r="K331" t="s" s="2">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="L331" t="s" s="2">
-        <v>1025</v>
+        <v>949</v>
       </c>
       <c r="M331" t="s" s="2">
-        <v>290</v>
+        <v>950</v>
       </c>
       <c r="N331" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O331" s="2"/>
+        <v>951</v>
+      </c>
+      <c r="O331" t="s" s="2">
+        <v>952</v>
+      </c>
       <c r="P331" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q331" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q331" s="2"/>
       <c r="R331" t="s" s="2">
         <v>84</v>
       </c>
@@ -48063,7 +48069,7 @@
         <v>84</v>
       </c>
       <c r="AF331" t="s" s="2">
-        <v>293</v>
+        <v>953</v>
       </c>
       <c r="AG331" t="s" s="2">
         <v>85</v>
@@ -48072,13 +48078,13 @@
         <v>102</v>
       </c>
       <c r="AI331" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ331" t="s" s="2">
         <v>114</v>
       </c>
       <c r="AK331" t="s" s="2">
-        <v>1026</v>
+        <v>84</v>
       </c>
       <c r="AL331" t="s" s="2">
         <v>84</v>
@@ -48099,10 +48105,10 @@
         <v>84</v>
       </c>
       <c r="AR331" t="s" s="2">
-        <v>295</v>
+        <v>954</v>
       </c>
       <c r="AS331" t="s" s="2">
-        <v>296</v>
+        <v>955</v>
       </c>
       <c r="AT331" t="s" s="2">
         <v>84</v>
@@ -48113,10 +48119,10 @@
     </row>
     <row r="332" hidden="true">
       <c r="A332" t="s" s="2">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" t="s" s="2">
@@ -48139,16 +48145,18 @@
         <v>84</v>
       </c>
       <c r="K332" t="s" s="2">
-        <v>558</v>
+        <v>271</v>
       </c>
       <c r="L332" t="s" s="2">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="M332" t="s" s="2">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="N332" s="2"/>
-      <c r="O332" s="2"/>
+      <c r="O332" t="s" s="2">
+        <v>862</v>
+      </c>
       <c r="P332" t="s" s="2">
         <v>84</v>
       </c>
@@ -48196,7 +48204,7 @@
         <v>84</v>
       </c>
       <c r="AF332" t="s" s="2">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="AG332" t="s" s="2">
         <v>85</v>
@@ -48235,10 +48243,10 @@
         <v>84</v>
       </c>
       <c r="AS332" t="s" s="2">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="AT332" t="s" s="2">
-        <v>84</v>
+        <v>864</v>
       </c>
       <c r="AU332" t="s" s="2">
         <v>84</v>
@@ -48246,14 +48254,12 @@
     </row>
     <row r="333" hidden="true">
       <c r="A333" t="s" s="2">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="C333" t="s" s="2">
-        <v>1029</v>
-      </c>
+        <v>959</v>
+      </c>
+      <c r="C333" s="2"/>
       <c r="D333" t="s" s="2">
         <v>84</v>
       </c>
@@ -48262,7 +48268,7 @@
         <v>85</v>
       </c>
       <c r="G333" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H333" t="s" s="2">
         <v>84</v>
@@ -48274,13 +48280,13 @@
         <v>84</v>
       </c>
       <c r="K333" t="s" s="2">
-        <v>833</v>
+        <v>116</v>
       </c>
       <c r="L333" t="s" s="2">
-        <v>834</v>
+        <v>117</v>
       </c>
       <c r="M333" t="s" s="2">
-        <v>835</v>
+        <v>118</v>
       </c>
       <c r="N333" s="2"/>
       <c r="O333" s="2"/>
@@ -48331,19 +48337,19 @@
         <v>84</v>
       </c>
       <c r="AF333" t="s" s="2">
-        <v>832</v>
+        <v>119</v>
       </c>
       <c r="AG333" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH333" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI333" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ333" t="s" s="2">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AK333" t="s" s="2">
         <v>84</v>
@@ -48367,13 +48373,13 @@
         <v>84</v>
       </c>
       <c r="AR333" t="s" s="2">
-        <v>837</v>
+        <v>84</v>
       </c>
       <c r="AS333" t="s" s="2">
-        <v>838</v>
+        <v>120</v>
       </c>
       <c r="AT333" t="s" s="2">
-        <v>839</v>
+        <v>84</v>
       </c>
       <c r="AU333" t="s" s="2">
         <v>84</v>
@@ -48381,21 +48387,21 @@
     </row>
     <row r="334" hidden="true">
       <c r="A334" t="s" s="2">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>840</v>
+        <v>961</v>
       </c>
       <c r="C334" s="2"/>
       <c r="D334" t="s" s="2">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E334" s="2"/>
       <c r="F334" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G334" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H334" t="s" s="2">
         <v>84</v>
@@ -48407,15 +48413,17 @@
         <v>84</v>
       </c>
       <c r="K334" t="s" s="2">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L334" t="s" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="M334" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N334" s="2"/>
+        <v>125</v>
+      </c>
+      <c r="N334" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="O334" s="2"/>
       <c r="P334" t="s" s="2">
         <v>84</v>
@@ -48452,31 +48460,31 @@
         <v>84</v>
       </c>
       <c r="AB334" t="s" s="2">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AC334" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="AD334" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE334" t="s" s="2">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="AF334" t="s" s="2">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="AG334" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH334" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI334" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ334" t="s" s="2">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="AK334" t="s" s="2">
         <v>84</v>
@@ -48514,21 +48522,21 @@
     </row>
     <row r="335" hidden="true">
       <c r="A335" t="s" s="2">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>841</v>
+        <v>963</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" t="s" s="2">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="E335" s="2"/>
       <c r="F335" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G335" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H335" t="s" s="2">
         <v>84</v>
@@ -48537,19 +48545,19 @@
         <v>84</v>
       </c>
       <c r="J335" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K335" t="s" s="2">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="L335" t="s" s="2">
-        <v>124</v>
+        <v>1027</v>
       </c>
       <c r="M335" t="s" s="2">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="N335" t="s" s="2">
-        <v>126</v>
+        <v>281</v>
       </c>
       <c r="O335" s="2"/>
       <c r="P335" t="s" s="2">
@@ -48599,22 +48607,22 @@
         <v>84</v>
       </c>
       <c r="AF335" t="s" s="2">
-        <v>130</v>
+        <v>282</v>
       </c>
       <c r="AG335" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH335" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI335" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AJ335" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK335" t="s" s="2">
-        <v>84</v>
+        <v>1028</v>
       </c>
       <c r="AL335" t="s" s="2">
         <v>84</v>
@@ -48635,10 +48643,10 @@
         <v>84</v>
       </c>
       <c r="AR335" t="s" s="2">
-        <v>84</v>
+        <v>285</v>
       </c>
       <c r="AS335" t="s" s="2">
-        <v>120</v>
+        <v>286</v>
       </c>
       <c r="AT335" t="s" s="2">
         <v>84</v>
@@ -48649,50 +48657,50 @@
     </row>
     <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>842</v>
+        <v>967</v>
       </c>
       <c r="C336" s="2"/>
       <c r="D336" t="s" s="2">
-        <v>843</v>
+        <v>84</v>
       </c>
       <c r="E336" s="2"/>
       <c r="F336" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G336" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H336" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I336" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="J336" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K336" t="s" s="2">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="L336" t="s" s="2">
-        <v>844</v>
+        <v>1030</v>
       </c>
       <c r="M336" t="s" s="2">
-        <v>845</v>
+        <v>290</v>
       </c>
       <c r="N336" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O336" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O336" s="2"/>
       <c r="P336" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q336" s="2"/>
+      <c r="Q336" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="R336" t="s" s="2">
         <v>84</v>
       </c>
@@ -48736,22 +48744,22 @@
         <v>84</v>
       </c>
       <c r="AF336" t="s" s="2">
-        <v>846</v>
+        <v>293</v>
       </c>
       <c r="AG336" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH336" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI336" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AJ336" t="s" s="2">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="AK336" t="s" s="2">
-        <v>84</v>
+        <v>1031</v>
       </c>
       <c r="AL336" t="s" s="2">
         <v>84</v>
@@ -48772,10 +48780,10 @@
         <v>84</v>
       </c>
       <c r="AR336" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AS336" t="s" s="2">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="AT336" t="s" s="2">
         <v>84</v>
@@ -48786,10 +48794,10 @@
     </row>
     <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" t="s" s="2">
@@ -48800,7 +48808,7 @@
         <v>85</v>
       </c>
       <c r="G337" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H337" t="s" s="2">
         <v>84</v>
@@ -48812,18 +48820,16 @@
         <v>84</v>
       </c>
       <c r="K337" t="s" s="2">
-        <v>488</v>
+        <v>558</v>
       </c>
       <c r="L337" t="s" s="2">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="M337" t="s" s="2">
-        <v>849</v>
+        <v>867</v>
       </c>
       <c r="N337" s="2"/>
-      <c r="O337" t="s" s="2">
-        <v>850</v>
-      </c>
+      <c r="O337" s="2"/>
       <c r="P337" t="s" s="2">
         <v>84</v>
       </c>
@@ -48871,13 +48877,13 @@
         <v>84</v>
       </c>
       <c r="AF337" t="s" s="2">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="AG337" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH337" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="AI337" t="s" s="2">
         <v>84</v>
@@ -48910,7 +48916,7 @@
         <v>84</v>
       </c>
       <c r="AS337" t="s" s="2">
-        <v>851</v>
+        <v>868</v>
       </c>
       <c r="AT337" t="s" s="2">
         <v>84</v>
@@ -48919,26 +48925,28 @@
         <v>84</v>
       </c>
     </row>
-    <row r="338">
+    <row r="338" hidden="true">
       <c r="A338" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="B338" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="C338" t="s" s="2">
         <v>1034</v>
       </c>
-      <c r="B338" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="C338" s="2"/>
       <c r="D338" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E338" s="2"/>
       <c r="F338" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G338" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H338" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I338" t="s" s="2">
         <v>84</v>
@@ -48947,13 +48955,13 @@
         <v>84</v>
       </c>
       <c r="K338" t="s" s="2">
-        <v>251</v>
+        <v>833</v>
       </c>
       <c r="L338" t="s" s="2">
-        <v>853</v>
+        <v>834</v>
       </c>
       <c r="M338" t="s" s="2">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="N338" s="2"/>
       <c r="O338" s="2"/>
@@ -48980,13 +48988,13 @@
         <v>84</v>
       </c>
       <c r="X338" t="s" s="2">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="Y338" t="s" s="2">
-        <v>855</v>
+        <v>84</v>
       </c>
       <c r="Z338" t="s" s="2">
-        <v>856</v>
+        <v>84</v>
       </c>
       <c r="AA338" t="s" s="2">
         <v>84</v>
@@ -49004,13 +49012,13 @@
         <v>84</v>
       </c>
       <c r="AF338" t="s" s="2">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="AH338" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI338" t="s" s="2">
         <v>84</v>
@@ -49028,7 +49036,7 @@
         <v>84</v>
       </c>
       <c r="AN338" t="s" s="2">
-        <v>857</v>
+        <v>84</v>
       </c>
       <c r="AO338" t="s" s="2">
         <v>84</v>
@@ -49040,13 +49048,13 @@
         <v>84</v>
       </c>
       <c r="AR338" t="s" s="2">
-        <v>84</v>
+        <v>837</v>
       </c>
       <c r="AS338" t="s" s="2">
         <v>838</v>
       </c>
       <c r="AT338" t="s" s="2">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="AU338" t="s" s="2">
         <v>84</v>
@@ -49057,7 +49065,7 @@
         <v>1035</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>921</v>
+        <v>840</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" t="s" s="2">
@@ -49190,7 +49198,7 @@
         <v>1036</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>923</v>
+        <v>841</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" t="s" s="2">
@@ -49260,16 +49268,16 @@
         <v>84</v>
       </c>
       <c r="AB340" t="s" s="2">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="AC340" t="s" s="2">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="AD340" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE340" t="s" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="AF340" t="s" s="2">
         <v>130</v>
@@ -49325,11 +49333,11 @@
         <v>1037</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>925</v>
+        <v>842</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" t="s" s="2">
-        <v>84</v>
+        <v>843</v>
       </c>
       <c r="E341" s="2"/>
       <c r="F341" t="s" s="2">
@@ -49342,25 +49350,25 @@
         <v>84</v>
       </c>
       <c r="I341" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J341" t="s" s="2">
         <v>103</v>
       </c>
       <c r="K341" t="s" s="2">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="L341" t="s" s="2">
-        <v>926</v>
+        <v>844</v>
       </c>
       <c r="M341" t="s" s="2">
-        <v>927</v>
+        <v>845</v>
       </c>
       <c r="N341" t="s" s="2">
-        <v>928</v>
+        <v>126</v>
       </c>
       <c r="O341" t="s" s="2">
-        <v>929</v>
+        <v>485</v>
       </c>
       <c r="P341" t="s" s="2">
         <v>84</v>
@@ -49385,11 +49393,13 @@
         <v>84</v>
       </c>
       <c r="X341" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y341" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y341" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z341" t="s" s="2">
-        <v>1038</v>
+        <v>84</v>
       </c>
       <c r="AA341" t="s" s="2">
         <v>84</v>
@@ -49407,7 +49417,7 @@
         <v>84</v>
       </c>
       <c r="AF341" t="s" s="2">
-        <v>931</v>
+        <v>846</v>
       </c>
       <c r="AG341" t="s" s="2">
         <v>85</v>
@@ -49419,7 +49429,7 @@
         <v>84</v>
       </c>
       <c r="AJ341" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="AK341" t="s" s="2">
         <v>84</v>
@@ -49443,10 +49453,10 @@
         <v>84</v>
       </c>
       <c r="AR341" t="s" s="2">
-        <v>932</v>
+        <v>84</v>
       </c>
       <c r="AS341" t="s" s="2">
-        <v>933</v>
+        <v>216</v>
       </c>
       <c r="AT341" t="s" s="2">
         <v>84</v>
@@ -49457,10 +49467,10 @@
     </row>
     <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>940</v>
+        <v>847</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" t="s" s="2">
@@ -49471,7 +49481,7 @@
         <v>85</v>
       </c>
       <c r="G342" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H342" t="s" s="2">
         <v>84</v>
@@ -49480,22 +49490,20 @@
         <v>84</v>
       </c>
       <c r="J342" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K342" t="s" s="2">
-        <v>116</v>
+        <v>488</v>
       </c>
       <c r="L342" t="s" s="2">
-        <v>941</v>
+        <v>848</v>
       </c>
       <c r="M342" t="s" s="2">
-        <v>942</v>
-      </c>
-      <c r="N342" t="s" s="2">
-        <v>943</v>
-      </c>
+        <v>849</v>
+      </c>
+      <c r="N342" s="2"/>
       <c r="O342" t="s" s="2">
-        <v>944</v>
+        <v>850</v>
       </c>
       <c r="P342" t="s" s="2">
         <v>84</v>
@@ -49544,13 +49552,13 @@
         <v>84</v>
       </c>
       <c r="AF342" t="s" s="2">
-        <v>945</v>
+        <v>847</v>
       </c>
       <c r="AG342" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH342" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI342" t="s" s="2">
         <v>84</v>
@@ -49580,10 +49588,10 @@
         <v>84</v>
       </c>
       <c r="AR342" t="s" s="2">
-        <v>946</v>
+        <v>84</v>
       </c>
       <c r="AS342" t="s" s="2">
-        <v>947</v>
+        <v>851</v>
       </c>
       <c r="AT342" t="s" s="2">
         <v>84</v>
@@ -49594,10 +49602,10 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" t="s" s="2">
@@ -49605,7 +49613,7 @@
       </c>
       <c r="E343" s="2"/>
       <c r="F343" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G343" t="s" s="2">
         <v>102</v>
@@ -49620,18 +49628,16 @@
         <v>84</v>
       </c>
       <c r="K343" t="s" s="2">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="L343" t="s" s="2">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="N343" s="2"/>
-      <c r="O343" t="s" s="2">
-        <v>862</v>
-      </c>
+      <c r="O343" s="2"/>
       <c r="P343" t="s" s="2">
         <v>84</v>
       </c>
@@ -49655,13 +49661,13 @@
         <v>84</v>
       </c>
       <c r="X343" t="s" s="2">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="Y343" t="s" s="2">
-        <v>84</v>
+        <v>855</v>
       </c>
       <c r="Z343" t="s" s="2">
-        <v>84</v>
+        <v>856</v>
       </c>
       <c r="AA343" t="s" s="2">
         <v>84</v>
@@ -49679,10 +49685,10 @@
         <v>84</v>
       </c>
       <c r="AF343" t="s" s="2">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="AG343" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="AH343" t="s" s="2">
         <v>102</v>
@@ -49703,7 +49709,7 @@
         <v>84</v>
       </c>
       <c r="AN343" t="s" s="2">
-        <v>84</v>
+        <v>857</v>
       </c>
       <c r="AO343" t="s" s="2">
         <v>84</v>
@@ -49718,10 +49724,10 @@
         <v>84</v>
       </c>
       <c r="AS343" t="s" s="2">
-        <v>863</v>
+        <v>838</v>
       </c>
       <c r="AT343" t="s" s="2">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="AU343" t="s" s="2">
         <v>84</v>
@@ -49729,10 +49735,10 @@
     </row>
     <row r="344" hidden="true">
       <c r="A344" t="s" s="2">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>951</v>
+        <v>929</v>
       </c>
       <c r="C344" s="2"/>
       <c r="D344" t="s" s="2">
@@ -49862,10 +49868,10 @@
     </row>
     <row r="345" hidden="true">
       <c r="A345" t="s" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>953</v>
+        <v>931</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" t="s" s="2">
@@ -49997,10 +50003,10 @@
     </row>
     <row r="346" hidden="true">
       <c r="A346" t="s" s="2">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>955</v>
+        <v>933</v>
       </c>
       <c r="C346" s="2"/>
       <c r="D346" t="s" s="2">
@@ -50011,7 +50017,7 @@
         <v>85</v>
       </c>
       <c r="G346" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H346" t="s" s="2">
         <v>84</v>
@@ -50023,18 +50029,20 @@
         <v>103</v>
       </c>
       <c r="K346" t="s" s="2">
-        <v>278</v>
+        <v>171</v>
       </c>
       <c r="L346" t="s" s="2">
-        <v>1044</v>
+        <v>934</v>
       </c>
       <c r="M346" t="s" s="2">
-        <v>280</v>
+        <v>935</v>
       </c>
       <c r="N346" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O346" s="2"/>
+        <v>936</v>
+      </c>
+      <c r="O346" t="s" s="2">
+        <v>937</v>
+      </c>
       <c r="P346" t="s" s="2">
         <v>84</v>
       </c>
@@ -50058,13 +50066,11 @@
         <v>84</v>
       </c>
       <c r="X346" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y346" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y346" s="2"/>
       <c r="Z346" t="s" s="2">
-        <v>84</v>
+        <v>1043</v>
       </c>
       <c r="AA346" t="s" s="2">
         <v>84</v>
@@ -50082,16 +50088,16 @@
         <v>84</v>
       </c>
       <c r="AF346" t="s" s="2">
-        <v>282</v>
+        <v>939</v>
       </c>
       <c r="AG346" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AH346" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AI346" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ346" t="s" s="2">
         <v>114</v>
@@ -50118,10 +50124,10 @@
         <v>84</v>
       </c>
       <c r="AR346" t="s" s="2">
-        <v>285</v>
+        <v>940</v>
       </c>
       <c r="AS346" t="s" s="2">
-        <v>286</v>
+        <v>941</v>
       </c>
       <c r="AT346" t="s" s="2">
         <v>84</v>
@@ -50132,10 +50138,10 @@
     </row>
     <row r="347" hidden="true">
       <c r="A347" t="s" s="2">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="C347" s="2"/>
       <c r="D347" t="s" s="2">
@@ -50158,24 +50164,24 @@
         <v>103</v>
       </c>
       <c r="K347" t="s" s="2">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="L347" t="s" s="2">
-        <v>1046</v>
+        <v>949</v>
       </c>
       <c r="M347" t="s" s="2">
-        <v>290</v>
+        <v>950</v>
       </c>
       <c r="N347" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O347" s="2"/>
+        <v>951</v>
+      </c>
+      <c r="O347" t="s" s="2">
+        <v>952</v>
+      </c>
       <c r="P347" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q347" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q347" s="2"/>
       <c r="R347" t="s" s="2">
         <v>84</v>
       </c>
@@ -50219,7 +50225,7 @@
         <v>84</v>
       </c>
       <c r="AF347" t="s" s="2">
-        <v>293</v>
+        <v>953</v>
       </c>
       <c r="AG347" t="s" s="2">
         <v>85</v>
@@ -50228,7 +50234,7 @@
         <v>102</v>
       </c>
       <c r="AI347" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AJ347" t="s" s="2">
         <v>114</v>
@@ -50255,10 +50261,10 @@
         <v>84</v>
       </c>
       <c r="AR347" t="s" s="2">
-        <v>295</v>
+        <v>954</v>
       </c>
       <c r="AS347" t="s" s="2">
-        <v>296</v>
+        <v>955</v>
       </c>
       <c r="AT347" t="s" s="2">
         <v>84</v>
@@ -50267,12 +50273,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="348" hidden="true">
+    <row r="348">
       <c r="A348" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="C348" s="2"/>
       <c r="D348" t="s" s="2">
@@ -50286,7 +50292,7 @@
         <v>102</v>
       </c>
       <c r="H348" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I348" t="s" s="2">
         <v>84</v>
@@ -50295,16 +50301,18 @@
         <v>84</v>
       </c>
       <c r="K348" t="s" s="2">
-        <v>558</v>
+        <v>271</v>
       </c>
       <c r="L348" t="s" s="2">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="M348" t="s" s="2">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="N348" s="2"/>
-      <c r="O348" s="2"/>
+      <c r="O348" t="s" s="2">
+        <v>862</v>
+      </c>
       <c r="P348" t="s" s="2">
         <v>84</v>
       </c>
@@ -50352,7 +50360,7 @@
         <v>84</v>
       </c>
       <c r="AF348" t="s" s="2">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="AG348" t="s" s="2">
         <v>85</v>
@@ -50391,21 +50399,21 @@
         <v>84</v>
       </c>
       <c r="AS348" t="s" s="2">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="AT348" t="s" s="2">
-        <v>84</v>
+        <v>864</v>
       </c>
       <c r="AU348" t="s" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" hidden="true">
       <c r="A349" t="s" s="2">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>1048</v>
+        <v>959</v>
       </c>
       <c r="C349" s="2"/>
       <c r="D349" t="s" s="2">
@@ -50416,10 +50424,10 @@
         <v>85</v>
       </c>
       <c r="G349" t="s" s="2">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H349" t="s" s="2">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="I349" t="s" s="2">
         <v>84</v>
@@ -50428,20 +50436,16 @@
         <v>84</v>
       </c>
       <c r="K349" t="s" s="2">
-        <v>1049</v>
+        <v>116</v>
       </c>
       <c r="L349" t="s" s="2">
-        <v>1050</v>
+        <v>117</v>
       </c>
       <c r="M349" t="s" s="2">
-        <v>1051</v>
-      </c>
-      <c r="N349" t="s" s="2">
-        <v>1052</v>
-      </c>
-      <c r="O349" t="s" s="2">
-        <v>1053</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N349" s="2"/>
+      <c r="O349" s="2"/>
       <c r="P349" t="s" s="2">
         <v>84</v>
       </c>
@@ -50465,78 +50469,755 @@
         <v>84</v>
       </c>
       <c r="X349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF349" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG349" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH349" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS349" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AT349" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU349" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="350" hidden="true">
+      <c r="A350" t="s" s="2">
+        <v>1047</v>
+      </c>
+      <c r="B350" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="C350" s="2"/>
+      <c r="D350" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E350" s="2"/>
+      <c r="F350" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G350" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K350" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L350" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M350" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N350" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O350" s="2"/>
+      <c r="P350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q350" s="2"/>
+      <c r="R350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB350" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AC350" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AD350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE350" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AF350" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG350" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH350" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ350" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS350" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AT350" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU350" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="351" hidden="true">
+      <c r="A351" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="B351" t="s" s="2">
+        <v>963</v>
+      </c>
+      <c r="C351" s="2"/>
+      <c r="D351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E351" s="2"/>
+      <c r="F351" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G351" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J351" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K351" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L351" t="s" s="2">
+        <v>1049</v>
+      </c>
+      <c r="M351" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N351" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O351" s="2"/>
+      <c r="P351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q351" s="2"/>
+      <c r="R351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF351" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG351" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH351" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI351" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AJ351" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR351" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AS351" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AT351" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU351" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="352" hidden="true">
+      <c r="A352" t="s" s="2">
+        <v>1050</v>
+      </c>
+      <c r="B352" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="C352" s="2"/>
+      <c r="D352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E352" s="2"/>
+      <c r="F352" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G352" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J352" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K352" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L352" t="s" s="2">
+        <v>1051</v>
+      </c>
+      <c r="M352" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N352" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O352" s="2"/>
+      <c r="P352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q352" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="R352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF352" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AG352" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH352" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI352" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AJ352" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR352" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AS352" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AT352" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU352" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="353" hidden="true">
+      <c r="A353" t="s" s="2">
+        <v>1052</v>
+      </c>
+      <c r="B353" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="C353" s="2"/>
+      <c r="D353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E353" s="2"/>
+      <c r="F353" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G353" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="H353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K353" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L353" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="M353" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="N353" s="2"/>
+      <c r="O353" s="2"/>
+      <c r="P353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q353" s="2"/>
+      <c r="R353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF353" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="AG353" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH353" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ353" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS353" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="AT353" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU353" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s" s="2">
+        <v>1053</v>
+      </c>
+      <c r="B354" t="s" s="2">
+        <v>1053</v>
+      </c>
+      <c r="C354" s="2"/>
+      <c r="D354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E354" s="2"/>
+      <c r="F354" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G354" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H354" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K354" t="s" s="2">
+        <v>1054</v>
+      </c>
+      <c r="L354" t="s" s="2">
+        <v>1055</v>
+      </c>
+      <c r="M354" t="s" s="2">
+        <v>1056</v>
+      </c>
+      <c r="N354" t="s" s="2">
+        <v>1057</v>
+      </c>
+      <c r="O354" t="s" s="2">
+        <v>1058</v>
+      </c>
+      <c r="P354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q354" s="2"/>
+      <c r="R354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X354" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="Y349" s="2"/>
-      <c r="Z349" t="s" s="2">
-        <v>1054</v>
-      </c>
-      <c r="AA349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF349" t="s" s="2">
-        <v>1048</v>
-      </c>
-      <c r="AG349" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH349" t="s" s="2">
+      <c r="Y354" s="2"/>
+      <c r="Z354" t="s" s="2">
+        <v>1059</v>
+      </c>
+      <c r="AA354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF354" t="s" s="2">
+        <v>1053</v>
+      </c>
+      <c r="AG354" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH354" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="AI349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ349" t="s" s="2">
+      <c r="AI354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ354" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AK349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ349" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR349" t="s" s="2">
-        <v>1055</v>
-      </c>
-      <c r="AS349" t="s" s="2">
-        <v>1056</v>
-      </c>
-      <c r="AT349" t="s" s="2">
-        <v>1057</v>
-      </c>
-      <c r="AU349" t="s" s="2">
+      <c r="AK354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ354" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR354" t="s" s="2">
+        <v>1060</v>
+      </c>
+      <c r="AS354" t="s" s="2">
+        <v>1061</v>
+      </c>
+      <c r="AT354" t="s" s="2">
+        <v>1062</v>
+      </c>
+      <c r="AU354" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU349">
+  <autoFilter ref="A1:AU354">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -50546,7 +51227,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI348">
+  <conditionalFormatting sqref="A2:AI353">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -430,7 +430,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -729,7 +729,7 @@
     <t>as-ext-registration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-registration|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-registration|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1035,7 +1035,7 @@
     <t>as-ext-frpractitioner-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1177,7 +1177,7 @@
     <t>as-ext-smartcard</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-smartcard|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-smartcard|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1311,7 +1311,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2281,7 +2281,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2345,7 +2345,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2503,7 +2503,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -2741,7 +2741,7 @@
     <t>as-ext-education-level</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-education-level|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-education-level|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -3275,7 +3275,7 @@
     <t>Practitioner.communication</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed|1.2.0-snapshot-2}
+    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed|1.2.0-snapshot-3}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/main/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
